--- a/research/traditional_assets/database/data/malta/malta_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_beverage_alcoholic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08353296383407285</v>
+        <v>0.08326984846065361</v>
       </c>
       <c r="C2">
-        <v>266.3514752596608</v>
+        <v>265.4196933246249</v>
       </c>
       <c r="D2">
-        <v>263.7714752596608</v>
+        <v>265.6236933246249</v>
       </c>
       <c r="E2">
-        <v>-28.7</v>
+        <v>-25.916</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.784</v>
       </c>
       <c r="G2">
         <v>2.58</v>
@@ -1451,28 +1451,28 @@
         <v>20.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1400352</v>
       </c>
       <c r="N2">
-        <v>20.3</v>
+        <v>20.1599648</v>
       </c>
       <c r="O2">
-        <v>7.105</v>
+        <v>7.055987679999999</v>
       </c>
       <c r="P2">
-        <v>13.195</v>
+        <v>13.10397712</v>
       </c>
       <c r="Q2">
-        <v>22.395</v>
+        <v>22.30397712</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08353296383407285</v>
+        <v>0.08378070551581172</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6956299597949308</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>144.9635520212061</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08326984846065361</v>
+        <v>0.08300673308723434</v>
       </c>
       <c r="C3">
-        <v>265.4196933246249</v>
+        <v>264.5141081022473</v>
       </c>
       <c r="D3">
-        <v>265.6236933246249</v>
+        <v>267.5021081022473</v>
       </c>
       <c r="E3">
-        <v>-25.916</v>
+        <v>-23.132</v>
       </c>
       <c r="F3">
-        <v>2.784</v>
+        <v>5.568</v>
       </c>
       <c r="G3">
         <v>2.58</v>
@@ -1533,28 +1533,28 @@
         <v>20.3</v>
       </c>
       <c r="M3">
-        <v>0.1400352</v>
+        <v>0.2800703999999999</v>
       </c>
       <c r="N3">
-        <v>20.1599648</v>
+        <v>20.0199296</v>
       </c>
       <c r="O3">
-        <v>7.055987679999999</v>
+        <v>7.00697536</v>
       </c>
       <c r="P3">
-        <v>13.10397712</v>
+        <v>13.01295424</v>
       </c>
       <c r="Q3">
-        <v>22.30397712</v>
+        <v>22.21295424</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08378070551581172</v>
+        <v>0.08403350315023914</v>
       </c>
       <c r="T3">
-        <v>0.6956299597949308</v>
+        <v>0.700260037248331</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>144.9635520212061</v>
+        <v>72.48177601060307</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08300673308723434</v>
+        <v>0.0827436177138151</v>
       </c>
       <c r="C4">
-        <v>264.5141081022473</v>
+        <v>263.6352793177193</v>
       </c>
       <c r="D4">
-        <v>267.5021081022473</v>
+        <v>269.4072793177193</v>
       </c>
       <c r="E4">
-        <v>-23.132</v>
+        <v>-20.348</v>
       </c>
       <c r="F4">
-        <v>5.568</v>
+        <v>8.351999999999999</v>
       </c>
       <c r="G4">
         <v>2.58</v>
@@ -1615,28 +1615,28 @@
         <v>20.3</v>
       </c>
       <c r="M4">
-        <v>0.2800703999999999</v>
+        <v>0.4201055999999999</v>
       </c>
       <c r="N4">
-        <v>20.0199296</v>
+        <v>19.8798944</v>
       </c>
       <c r="O4">
-        <v>7.00697536</v>
+        <v>6.95796304</v>
       </c>
       <c r="P4">
-        <v>13.01295424</v>
+        <v>12.92193136</v>
       </c>
       <c r="Q4">
-        <v>22.21295424</v>
+        <v>22.12193136</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08403350315023914</v>
+        <v>0.08429151310702587</v>
       </c>
       <c r="T4">
-        <v>0.700260037248331</v>
+        <v>0.7049855802162343</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>72.48177601060307</v>
+        <v>48.32118400706871</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0827436177138151</v>
+        <v>0.08248050234039583</v>
       </c>
       <c r="C5">
-        <v>263.6352793177193</v>
+        <v>262.7837827562417</v>
       </c>
       <c r="D5">
-        <v>269.4072793177193</v>
+        <v>271.3397827562418</v>
       </c>
       <c r="E5">
-        <v>-20.348</v>
+        <v>-17.564</v>
       </c>
       <c r="F5">
-        <v>8.351999999999999</v>
+        <v>11.136</v>
       </c>
       <c r="G5">
         <v>2.58</v>
@@ -1697,28 +1697,28 @@
         <v>20.3</v>
       </c>
       <c r="M5">
-        <v>0.4201055999999999</v>
+        <v>0.5601407999999999</v>
       </c>
       <c r="N5">
-        <v>19.8798944</v>
+        <v>19.7398592</v>
       </c>
       <c r="O5">
-        <v>6.95796304</v>
+        <v>6.90895072</v>
       </c>
       <c r="P5">
-        <v>12.92193136</v>
+        <v>12.83090848</v>
       </c>
       <c r="Q5">
-        <v>22.12193136</v>
+        <v>22.03090848</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08429151310702587</v>
+        <v>0.08455489827124567</v>
       </c>
       <c r="T5">
-        <v>0.7049855802162343</v>
+        <v>0.7098095719959689</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.32118400706871</v>
+        <v>36.24088800530154</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08248050234039583</v>
+        <v>0.08221738696697659</v>
       </c>
       <c r="C6">
-        <v>262.7837827562417</v>
+        <v>261.9602108431922</v>
       </c>
       <c r="D6">
-        <v>271.3397827562418</v>
+        <v>273.3002108431922</v>
       </c>
       <c r="E6">
-        <v>-17.564</v>
+        <v>-14.78</v>
       </c>
       <c r="F6">
-        <v>11.136</v>
+        <v>13.92</v>
       </c>
       <c r="G6">
         <v>2.58</v>
@@ -1779,28 +1779,28 @@
         <v>20.3</v>
       </c>
       <c r="M6">
-        <v>0.5601407999999999</v>
+        <v>0.7001759999999999</v>
       </c>
       <c r="N6">
-        <v>19.7398592</v>
+        <v>19.599824</v>
       </c>
       <c r="O6">
-        <v>6.90895072</v>
+        <v>6.8599384</v>
       </c>
       <c r="P6">
-        <v>12.83090848</v>
+        <v>12.7398856</v>
       </c>
       <c r="Q6">
-        <v>22.03090848</v>
+        <v>21.9398856</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08455489827124567</v>
+        <v>0.08482382838629114</v>
       </c>
       <c r="T6">
-        <v>0.7098095719959689</v>
+        <v>0.7147351214973822</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.24088800530154</v>
+        <v>28.99271040424123</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08221738696697659</v>
+        <v>0.08195427159355732</v>
       </c>
       <c r="C7">
-        <v>261.9602108431922</v>
+        <v>261.1651732496257</v>
       </c>
       <c r="D7">
-        <v>273.3002108431922</v>
+        <v>275.2891732496257</v>
       </c>
       <c r="E7">
-        <v>-14.78</v>
+        <v>-11.996</v>
       </c>
       <c r="F7">
-        <v>13.92</v>
+        <v>16.704</v>
       </c>
       <c r="G7">
         <v>2.58</v>
@@ -1861,28 +1861,28 @@
         <v>20.3</v>
       </c>
       <c r="M7">
-        <v>0.7001759999999999</v>
+        <v>0.8402111999999999</v>
       </c>
       <c r="N7">
-        <v>19.599824</v>
+        <v>19.4597888</v>
       </c>
       <c r="O7">
-        <v>6.8599384</v>
+        <v>6.810926080000001</v>
       </c>
       <c r="P7">
-        <v>12.7398856</v>
+        <v>12.64886272</v>
       </c>
       <c r="Q7">
-        <v>21.9398856</v>
+        <v>21.84886272</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08482382838629114</v>
+        <v>0.08509848041867801</v>
       </c>
       <c r="T7">
-        <v>0.7147351214973822</v>
+        <v>0.7197654699243574</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.99271040424123</v>
+        <v>24.16059200353435</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08195427159355732</v>
+        <v>0.08169115622013808</v>
       </c>
       <c r="C8">
-        <v>261.1651732496257</v>
+        <v>260.3992975244076</v>
       </c>
       <c r="D8">
-        <v>275.2891732496257</v>
+        <v>277.3072975244076</v>
       </c>
       <c r="E8">
-        <v>-11.996</v>
+        <v>-9.212000000000003</v>
       </c>
       <c r="F8">
-        <v>16.704</v>
+        <v>19.488</v>
       </c>
       <c r="G8">
         <v>2.58</v>
@@ -1943,28 +1943,28 @@
         <v>20.3</v>
       </c>
       <c r="M8">
-        <v>0.8402111999999998</v>
+        <v>0.9802463999999997</v>
       </c>
       <c r="N8">
-        <v>19.4597888</v>
+        <v>19.3197536</v>
       </c>
       <c r="O8">
-        <v>6.810926080000001</v>
+        <v>6.761913760000001</v>
       </c>
       <c r="P8">
-        <v>12.64886272</v>
+        <v>12.55783984</v>
       </c>
       <c r="Q8">
-        <v>21.84886272</v>
+        <v>21.75783984</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08509848041867801</v>
+        <v>0.08537903894638502</v>
       </c>
       <c r="T8">
-        <v>0.7197654699243574</v>
+        <v>0.7249039978873966</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.16059200353436</v>
+        <v>20.70907886017231</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08169115622013806</v>
+        <v>0.08142804084671883</v>
       </c>
       <c r="C9">
-        <v>260.3992975244077</v>
+        <v>259.663229754359</v>
       </c>
       <c r="D9">
-        <v>277.3072975244077</v>
+        <v>279.355229754359</v>
       </c>
       <c r="E9">
-        <v>-9.212</v>
+        <v>-6.428000000000001</v>
       </c>
       <c r="F9">
-        <v>19.488</v>
+        <v>22.272</v>
       </c>
       <c r="G9">
         <v>2.58</v>
@@ -2025,28 +2025,28 @@
         <v>20.3</v>
       </c>
       <c r="M9">
-        <v>0.9802464</v>
+        <v>1.1202816</v>
       </c>
       <c r="N9">
-        <v>19.3197536</v>
+        <v>19.1797184</v>
       </c>
       <c r="O9">
-        <v>6.761913760000001</v>
+        <v>6.71290144</v>
       </c>
       <c r="P9">
-        <v>12.55783984</v>
+        <v>12.46681696</v>
       </c>
       <c r="Q9">
-        <v>21.75783984</v>
+        <v>21.66681696</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08537903894638502</v>
+        <v>0.08566569657252046</v>
       </c>
       <c r="T9">
-        <v>0.7249039978873966</v>
+        <v>0.7301542329800671</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.7090788601723</v>
+        <v>18.12044400265077</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08142804084671883</v>
+        <v>0.08116492547329958</v>
       </c>
       <c r="C10">
-        <v>259.663229754359</v>
+        <v>258.9576352538681</v>
       </c>
       <c r="D10">
-        <v>279.355229754359</v>
+        <v>281.4336352538681</v>
       </c>
       <c r="E10">
-        <v>-6.428000000000001</v>
+        <v>-3.644000000000002</v>
       </c>
       <c r="F10">
-        <v>22.272</v>
+        <v>25.056</v>
       </c>
       <c r="G10">
         <v>2.58</v>
@@ -2107,28 +2107,28 @@
         <v>20.3</v>
       </c>
       <c r="M10">
-        <v>1.1202816</v>
+        <v>1.2603168</v>
       </c>
       <c r="N10">
-        <v>19.1797184</v>
+        <v>19.0396832</v>
       </c>
       <c r="O10">
-        <v>6.71290144</v>
+        <v>6.66388912</v>
       </c>
       <c r="P10">
-        <v>12.46681696</v>
+        <v>12.37579408</v>
       </c>
       <c r="Q10">
-        <v>21.66681696</v>
+        <v>21.57579408</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08566569657252046</v>
+        <v>0.08595865436626327</v>
       </c>
       <c r="T10">
-        <v>0.7301542329800671</v>
+        <v>0.7355198578549942</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.12044400265077</v>
+        <v>16.10706133568957</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08116492547329958</v>
+        <v>0.08090181009988032</v>
       </c>
       <c r="C11">
-        <v>258.9576352538681</v>
+        <v>258.2831992855195</v>
       </c>
       <c r="D11">
-        <v>281.4336352538681</v>
+        <v>283.5431992855194</v>
       </c>
       <c r="E11">
-        <v>-3.644000000000002</v>
+        <v>-0.860000000000003</v>
       </c>
       <c r="F11">
-        <v>25.056</v>
+        <v>27.84</v>
       </c>
       <c r="G11">
         <v>2.58</v>
@@ -2189,28 +2189,28 @@
         <v>20.3</v>
       </c>
       <c r="M11">
-        <v>1.2603168</v>
+        <v>1.400352</v>
       </c>
       <c r="N11">
-        <v>19.0396832</v>
+        <v>18.899648</v>
       </c>
       <c r="O11">
-        <v>6.66388912</v>
+        <v>6.614876799999999</v>
       </c>
       <c r="P11">
-        <v>12.37579408</v>
+        <v>12.2847712</v>
       </c>
       <c r="Q11">
-        <v>21.57579408</v>
+        <v>21.4847712</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08595865436626327</v>
+        <v>0.08625812233320035</v>
       </c>
       <c r="T11">
-        <v>0.7355198578549942</v>
+        <v>0.7410047188382528</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.10706133568957</v>
+        <v>14.49635520212061</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08090181009988032</v>
+        <v>0.08063869472646107</v>
       </c>
       <c r="C12">
-        <v>258.2831992855195</v>
+        <v>257.640627813375</v>
       </c>
       <c r="D12">
-        <v>283.5431992855194</v>
+        <v>285.6846278133751</v>
       </c>
       <c r="E12">
-        <v>-0.8599999999999994</v>
+        <v>1.923999999999999</v>
       </c>
       <c r="F12">
-        <v>27.84</v>
+        <v>30.624</v>
       </c>
       <c r="G12">
         <v>2.58</v>
@@ -2271,28 +2271,28 @@
         <v>20.3</v>
       </c>
       <c r="M12">
-        <v>1.400352</v>
+        <v>1.5403872</v>
       </c>
       <c r="N12">
-        <v>18.899648</v>
+        <v>18.7596128</v>
       </c>
       <c r="O12">
-        <v>6.614876799999999</v>
+        <v>6.565864479999999</v>
       </c>
       <c r="P12">
-        <v>12.2847712</v>
+        <v>12.19374832</v>
       </c>
       <c r="Q12">
-        <v>21.4847712</v>
+        <v>21.39374832</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08625812233320035</v>
+        <v>0.08656431991737198</v>
       </c>
       <c r="T12">
-        <v>0.7410047188382528</v>
+        <v>0.7466128351245063</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.49635520212061</v>
+        <v>13.17850472920055</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08063869472646107</v>
+        <v>0.0804925793530418</v>
       </c>
       <c r="C13">
-        <v>257.640627813375</v>
+        <v>256.0598510055254</v>
       </c>
       <c r="D13">
-        <v>285.6846278133751</v>
+        <v>286.8878510055254</v>
       </c>
       <c r="E13">
-        <v>1.923999999999999</v>
+        <v>4.707999999999995</v>
       </c>
       <c r="F13">
-        <v>30.624</v>
+        <v>33.40799999999999</v>
       </c>
       <c r="G13">
         <v>2.58</v>
@@ -2353,45 +2353,45 @@
         <v>20.3</v>
       </c>
       <c r="M13">
-        <v>1.5403872</v>
+        <v>1.7305344</v>
       </c>
       <c r="N13">
-        <v>18.7596128</v>
+        <v>18.5694656</v>
       </c>
       <c r="O13">
-        <v>6.565864479999999</v>
+        <v>6.49931296</v>
       </c>
       <c r="P13">
-        <v>12.19374832</v>
+        <v>12.07015264</v>
       </c>
       <c r="Q13">
-        <v>21.39374832</v>
+        <v>21.27015264</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08656431991737198</v>
+        <v>0.0868774765375475</v>
       </c>
       <c r="T13">
-        <v>0.7466128351245063</v>
+        <v>0.7523484085990834</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.35</v>
       </c>
       <c r="W13">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.17850472920055</v>
+        <v>11.73048048048048</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0804925793530418</v>
+        <v>0.08023921397962254</v>
       </c>
       <c r="C14">
-        <v>256.0598510055254</v>
+        <v>255.3864522388309</v>
       </c>
       <c r="D14">
-        <v>286.8878510055254</v>
+        <v>288.998452238831</v>
       </c>
       <c r="E14">
-        <v>4.707999999999995</v>
+        <v>7.492000000000001</v>
       </c>
       <c r="F14">
-        <v>33.40799999999999</v>
+        <v>36.192</v>
       </c>
       <c r="G14">
         <v>2.58</v>
@@ -2435,28 +2435,28 @@
         <v>20.3</v>
       </c>
       <c r="M14">
-        <v>1.7305344</v>
+        <v>1.8747456</v>
       </c>
       <c r="N14">
-        <v>18.5694656</v>
+        <v>18.4252544</v>
       </c>
       <c r="O14">
-        <v>6.49931296</v>
+        <v>6.448839039999999</v>
       </c>
       <c r="P14">
-        <v>12.07015264</v>
+        <v>11.97641536</v>
       </c>
       <c r="Q14">
-        <v>21.27015264</v>
+        <v>21.17641536</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0868774765375475</v>
+        <v>0.08719783216048568</v>
       </c>
       <c r="T14">
-        <v>0.7523484085990834</v>
+        <v>0.758215834337444</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.73048048048048</v>
+        <v>10.82813582813583</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08023921397962254</v>
+        <v>0.07998584860620329</v>
       </c>
       <c r="C15">
-        <v>255.3864522388309</v>
+        <v>254.744338538409</v>
       </c>
       <c r="D15">
-        <v>288.998452238831</v>
+        <v>291.140338538409</v>
       </c>
       <c r="E15">
-        <v>7.492000000000001</v>
+        <v>10.276</v>
       </c>
       <c r="F15">
-        <v>36.192</v>
+        <v>38.976</v>
       </c>
       <c r="G15">
         <v>2.58</v>
@@ -2517,28 +2517,28 @@
         <v>20.3</v>
       </c>
       <c r="M15">
-        <v>1.8747456</v>
+        <v>2.0189568</v>
       </c>
       <c r="N15">
-        <v>18.4252544</v>
+        <v>18.2810432</v>
       </c>
       <c r="O15">
-        <v>6.448839039999999</v>
+        <v>6.398365119999999</v>
       </c>
       <c r="P15">
-        <v>11.97641536</v>
+        <v>11.88267808</v>
       </c>
       <c r="Q15">
-        <v>21.17641536</v>
+        <v>21.08267808</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08719783216048568</v>
+        <v>0.08752563791418988</v>
       </c>
       <c r="T15">
-        <v>0.758215834337444</v>
+        <v>0.764219711837162</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.82813582813583</v>
+        <v>10.05469755469755</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07998584860620329</v>
+        <v>0.07989823323278404</v>
       </c>
       <c r="C16">
-        <v>254.744338538409</v>
+        <v>252.7084233234565</v>
       </c>
       <c r="D16">
-        <v>291.140338538409</v>
+        <v>291.8884233234565</v>
       </c>
       <c r="E16">
-        <v>10.276</v>
+        <v>13.06000000000001</v>
       </c>
       <c r="F16">
-        <v>38.976</v>
+        <v>41.76000000000001</v>
       </c>
       <c r="G16">
         <v>2.58</v>
@@ -2599,45 +2599,45 @@
         <v>20.3</v>
       </c>
       <c r="M16">
-        <v>2.0189568</v>
+        <v>2.23416</v>
       </c>
       <c r="N16">
-        <v>18.2810432</v>
+        <v>18.06584</v>
       </c>
       <c r="O16">
-        <v>6.398365119999999</v>
+        <v>6.323044</v>
       </c>
       <c r="P16">
-        <v>11.88267808</v>
+        <v>11.742796</v>
       </c>
       <c r="Q16">
-        <v>21.08267808</v>
+        <v>20.942796</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08752563791418988</v>
+        <v>0.0878611567444518</v>
       </c>
       <c r="T16">
-        <v>0.764219711837162</v>
+        <v>0.7703648570427555</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.35</v>
       </c>
       <c r="W16">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.05469755469755</v>
+        <v>9.086188992731049</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07989823323278404</v>
+        <v>0.07965591785936478</v>
       </c>
       <c r="C17">
-        <v>252.7084233234565</v>
+        <v>252.0135426493064</v>
       </c>
       <c r="D17">
-        <v>291.8884233234565</v>
+        <v>293.9775426493064</v>
       </c>
       <c r="E17">
-        <v>13.06</v>
+        <v>15.844</v>
       </c>
       <c r="F17">
-        <v>41.76</v>
+        <v>44.544</v>
       </c>
       <c r="G17">
         <v>2.58</v>
@@ -2681,28 +2681,28 @@
         <v>20.3</v>
       </c>
       <c r="M17">
-        <v>2.23416</v>
+        <v>2.383104</v>
       </c>
       <c r="N17">
-        <v>18.06584</v>
+        <v>17.916896</v>
       </c>
       <c r="O17">
-        <v>6.323044</v>
+        <v>6.2709136</v>
       </c>
       <c r="P17">
-        <v>11.742796</v>
+        <v>11.6459824</v>
       </c>
       <c r="Q17">
-        <v>20.942796</v>
+        <v>20.8459824</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0878611567444518</v>
+        <v>0.08820466411829141</v>
       </c>
       <c r="T17">
-        <v>0.7703648570427555</v>
+        <v>0.7766563152294346</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.086188992731051</v>
+        <v>8.51830218068536</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07965591785936478</v>
+        <v>0.07941360248594551</v>
       </c>
       <c r="C18">
-        <v>252.0135426493064</v>
+        <v>251.3487822652842</v>
       </c>
       <c r="D18">
-        <v>293.9775426493064</v>
+        <v>296.0967822652842</v>
       </c>
       <c r="E18">
-        <v>15.844</v>
+        <v>18.628</v>
       </c>
       <c r="F18">
-        <v>44.544</v>
+        <v>47.328</v>
       </c>
       <c r="G18">
         <v>2.58</v>
@@ -2763,28 +2763,28 @@
         <v>20.3</v>
       </c>
       <c r="M18">
-        <v>2.383104</v>
+        <v>2.532048</v>
       </c>
       <c r="N18">
-        <v>17.916896</v>
+        <v>17.767952</v>
       </c>
       <c r="O18">
-        <v>6.2709136</v>
+        <v>6.2187832</v>
       </c>
       <c r="P18">
-        <v>11.6459824</v>
+        <v>11.5491688</v>
       </c>
       <c r="Q18">
-        <v>20.8459824</v>
+        <v>20.7491688</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08820466411829141</v>
+        <v>0.08855644877824762</v>
       </c>
       <c r="T18">
-        <v>0.7766563152294346</v>
+        <v>0.7830993748182024</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.51830218068536</v>
+        <v>8.017225581821513</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07941360248594551</v>
+        <v>0.07926488711252627</v>
       </c>
       <c r="C19">
-        <v>251.3487822652842</v>
+        <v>249.8806134944394</v>
       </c>
       <c r="D19">
-        <v>296.0967822652842</v>
+        <v>297.4126134944394</v>
       </c>
       <c r="E19">
-        <v>18.628</v>
+        <v>21.412</v>
       </c>
       <c r="F19">
-        <v>47.328</v>
+        <v>50.112</v>
       </c>
       <c r="G19">
         <v>2.58</v>
@@ -2845,45 +2845,45 @@
         <v>20.3</v>
       </c>
       <c r="M19">
-        <v>2.532048</v>
+        <v>2.7210816</v>
       </c>
       <c r="N19">
-        <v>17.767952</v>
+        <v>17.5789184</v>
       </c>
       <c r="O19">
-        <v>6.2187832</v>
+        <v>6.152621439999999</v>
       </c>
       <c r="P19">
-        <v>11.5491688</v>
+        <v>11.42629696</v>
       </c>
       <c r="Q19">
-        <v>20.7491688</v>
+        <v>20.62629696</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08855644877824762</v>
+        <v>0.0889168135518613</v>
       </c>
       <c r="T19">
-        <v>0.7830993748182024</v>
+        <v>0.789699582201818</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>8.017225581821513</v>
+        <v>7.460268740195074</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07926488711252627</v>
+        <v>0.07902777173910704</v>
       </c>
       <c r="C20">
-        <v>249.8806134944394</v>
+        <v>249.2189677546658</v>
       </c>
       <c r="D20">
-        <v>297.4126134944394</v>
+        <v>299.5349677546658</v>
       </c>
       <c r="E20">
-        <v>21.412</v>
+        <v>24.19599999999999</v>
       </c>
       <c r="F20">
-        <v>50.11199999999999</v>
+        <v>52.89599999999999</v>
       </c>
       <c r="G20">
         <v>2.58</v>
@@ -2927,28 +2927,28 @@
         <v>20.3</v>
       </c>
       <c r="M20">
-        <v>2.7210816</v>
+        <v>2.8722528</v>
       </c>
       <c r="N20">
-        <v>17.5789184</v>
+        <v>17.4277472</v>
       </c>
       <c r="O20">
-        <v>6.152621439999999</v>
+        <v>6.09971152</v>
       </c>
       <c r="P20">
-        <v>11.42629696</v>
+        <v>11.32803568</v>
       </c>
       <c r="Q20">
-        <v>20.62629696</v>
+        <v>20.52803568</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0889168135518613</v>
+        <v>0.08928607622111978</v>
       </c>
       <c r="T20">
-        <v>0.789699582201818</v>
+        <v>0.79646275766898</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.460268740195076</v>
+        <v>7.067623017026915</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07902777173910704</v>
+        <v>0.07879065636568777</v>
       </c>
       <c r="C21">
-        <v>249.2189677546658</v>
+        <v>248.5878302180251</v>
       </c>
       <c r="D21">
-        <v>299.5349677546658</v>
+        <v>301.6878302180251</v>
       </c>
       <c r="E21">
-        <v>24.19599999999999</v>
+        <v>26.98</v>
       </c>
       <c r="F21">
-        <v>52.89599999999999</v>
+        <v>55.68</v>
       </c>
       <c r="G21">
         <v>2.58</v>
@@ -3009,28 +3009,28 @@
         <v>20.3</v>
       </c>
       <c r="M21">
-        <v>2.8722528</v>
+        <v>3.023424</v>
       </c>
       <c r="N21">
-        <v>17.4277472</v>
+        <v>17.276576</v>
       </c>
       <c r="O21">
-        <v>6.09971152</v>
+        <v>6.0468016</v>
       </c>
       <c r="P21">
-        <v>11.32803568</v>
+        <v>11.2297744</v>
       </c>
       <c r="Q21">
-        <v>20.52803568</v>
+        <v>20.4297744</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08928607622111978</v>
+        <v>0.08966457045710971</v>
       </c>
       <c r="T21">
-        <v>0.79646275766898</v>
+        <v>0.8033950125228209</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.067623017026915</v>
+        <v>6.714241866175569</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07879065636568777</v>
+        <v>0.07855354099226851</v>
       </c>
       <c r="C22">
-        <v>248.5878302180251</v>
+        <v>247.9878634660663</v>
       </c>
       <c r="D22">
-        <v>301.6878302180251</v>
+        <v>303.8718634660663</v>
       </c>
       <c r="E22">
-        <v>26.98</v>
+        <v>29.764</v>
       </c>
       <c r="F22">
-        <v>55.68</v>
+        <v>58.464</v>
       </c>
       <c r="G22">
         <v>2.58</v>
@@ -3091,28 +3091,28 @@
         <v>20.3</v>
       </c>
       <c r="M22">
-        <v>3.023424</v>
+        <v>3.1745952</v>
       </c>
       <c r="N22">
-        <v>17.276576</v>
+        <v>17.1254048</v>
       </c>
       <c r="O22">
-        <v>6.0468016</v>
+        <v>5.99389168</v>
       </c>
       <c r="P22">
-        <v>11.2297744</v>
+        <v>11.13151312</v>
       </c>
       <c r="Q22">
-        <v>20.4297744</v>
+        <v>20.33151312</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08966457045710971</v>
+        <v>0.09005264682565634</v>
       </c>
       <c r="T22">
-        <v>0.8033950125228209</v>
+        <v>0.8105027674995438</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.714241866175569</v>
+        <v>6.39451606302435</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07855354099226851</v>
+        <v>0.07845942561884925</v>
       </c>
       <c r="C23">
-        <v>247.9878634660663</v>
+        <v>246.0795375895331</v>
       </c>
       <c r="D23">
-        <v>303.8718634660663</v>
+        <v>304.7475375895331</v>
       </c>
       <c r="E23">
-        <v>29.76399999999999</v>
+        <v>32.548</v>
       </c>
       <c r="F23">
-        <v>58.46399999999999</v>
+        <v>61.248</v>
       </c>
       <c r="G23">
         <v>2.58</v>
@@ -3173,45 +3173,45 @@
         <v>20.3</v>
       </c>
       <c r="M23">
-        <v>3.1745952</v>
+        <v>3.3870144</v>
       </c>
       <c r="N23">
-        <v>17.1254048</v>
+        <v>16.9129856</v>
       </c>
       <c r="O23">
-        <v>5.99389168</v>
+        <v>5.91954496</v>
       </c>
       <c r="P23">
-        <v>11.13151312</v>
+        <v>10.99344064</v>
       </c>
       <c r="Q23">
-        <v>20.33151312</v>
+        <v>20.19344064</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09005264682565634</v>
+        <v>0.09045067387031955</v>
       </c>
       <c r="T23">
-        <v>0.8105027674995438</v>
+        <v>0.817792772603875</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.35</v>
       </c>
       <c r="W23">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.394516063024351</v>
+        <v>5.993479094744917</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07845942561884925</v>
+        <v>0.07822881024543001</v>
       </c>
       <c r="C24">
-        <v>246.0795375895331</v>
+        <v>245.4627298684947</v>
       </c>
       <c r="D24">
-        <v>304.7475375895331</v>
+        <v>306.9147298684947</v>
       </c>
       <c r="E24">
-        <v>32.548</v>
+        <v>35.33199999999999</v>
       </c>
       <c r="F24">
-        <v>61.248</v>
+        <v>64.032</v>
       </c>
       <c r="G24">
         <v>2.58</v>
@@ -3255,28 +3255,28 @@
         <v>20.3</v>
       </c>
       <c r="M24">
-        <v>3.3870144</v>
+        <v>3.5409696</v>
       </c>
       <c r="N24">
-        <v>16.9129856</v>
+        <v>16.7590304</v>
       </c>
       <c r="O24">
-        <v>5.91954496</v>
+        <v>5.86566064</v>
       </c>
       <c r="P24">
-        <v>10.99344064</v>
+        <v>10.89336976</v>
       </c>
       <c r="Q24">
-        <v>20.19344064</v>
+        <v>20.09336976</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09045067387031955</v>
+        <v>0.09085903927977922</v>
       </c>
       <c r="T24">
-        <v>0.817792772603875</v>
+        <v>0.8252721284901369</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.993479094744917</v>
+        <v>5.732893047147313</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07822881024543001</v>
+        <v>0.07799819487201075</v>
       </c>
       <c r="C25">
-        <v>245.4627298684947</v>
+        <v>244.8769666118228</v>
       </c>
       <c r="D25">
-        <v>306.9147298684947</v>
+        <v>309.1129666118228</v>
       </c>
       <c r="E25">
-        <v>35.33199999999999</v>
+        <v>38.116</v>
       </c>
       <c r="F25">
-        <v>64.032</v>
+        <v>66.816</v>
       </c>
       <c r="G25">
         <v>2.58</v>
@@ -3337,28 +3337,28 @@
         <v>20.3</v>
       </c>
       <c r="M25">
-        <v>3.5409696</v>
+        <v>3.6949248</v>
       </c>
       <c r="N25">
-        <v>16.7590304</v>
+        <v>16.6050752</v>
       </c>
       <c r="O25">
-        <v>5.86566064</v>
+        <v>5.81177632</v>
       </c>
       <c r="P25">
-        <v>10.89336976</v>
+        <v>10.79329888</v>
       </c>
       <c r="Q25">
-        <v>20.09336976</v>
+        <v>19.99329888</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09085903927977922</v>
+        <v>0.09127815114738255</v>
       </c>
       <c r="T25">
-        <v>0.8252721284901369</v>
+        <v>0.8329483095313003</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.732893047147313</v>
+        <v>5.494022503516175</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07799819487201075</v>
+        <v>0.07776757949859148</v>
       </c>
       <c r="C26">
-        <v>244.8769666118228</v>
+        <v>244.3229196874714</v>
       </c>
       <c r="D26">
-        <v>309.1129666118228</v>
+        <v>311.3429196874714</v>
       </c>
       <c r="E26">
-        <v>38.11599999999999</v>
+        <v>40.89999999999999</v>
       </c>
       <c r="F26">
-        <v>66.81599999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G26">
         <v>2.58</v>
@@ -3419,28 +3419,28 @@
         <v>20.3</v>
       </c>
       <c r="M26">
-        <v>3.694924799999999</v>
+        <v>3.84888</v>
       </c>
       <c r="N26">
-        <v>16.6050752</v>
+        <v>16.45112</v>
       </c>
       <c r="O26">
-        <v>5.81177632</v>
+        <v>5.757891999999999</v>
       </c>
       <c r="P26">
-        <v>10.79329888</v>
+        <v>10.693228</v>
       </c>
       <c r="Q26">
-        <v>19.99329888</v>
+        <v>19.893228</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09127815114738255</v>
+        <v>0.09170843933145531</v>
       </c>
       <c r="T26">
-        <v>0.8329483095313003</v>
+        <v>0.8408291887335616</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.494022503516176</v>
+        <v>5.274261603375527</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07776757949859148</v>
+        <v>0.07753696412517223</v>
       </c>
       <c r="C27">
-        <v>244.3229196874714</v>
+        <v>243.8012804917997</v>
       </c>
       <c r="D27">
-        <v>311.3429196874714</v>
+        <v>313.6052804917997</v>
       </c>
       <c r="E27">
-        <v>40.89999999999999</v>
+        <v>43.684</v>
       </c>
       <c r="F27">
-        <v>69.59999999999999</v>
+        <v>72.384</v>
       </c>
       <c r="G27">
         <v>2.58</v>
@@ -3501,28 +3501,28 @@
         <v>20.3</v>
       </c>
       <c r="M27">
-        <v>3.84888</v>
+        <v>4.0028352</v>
       </c>
       <c r="N27">
-        <v>16.45112</v>
+        <v>16.2971648</v>
       </c>
       <c r="O27">
-        <v>5.757891999999999</v>
+        <v>5.70400768</v>
       </c>
       <c r="P27">
-        <v>10.693228</v>
+        <v>10.59315712</v>
       </c>
       <c r="Q27">
-        <v>19.893228</v>
+        <v>19.79315712</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09170843933145531</v>
+        <v>0.09215035692590842</v>
       </c>
       <c r="T27">
-        <v>0.8408291887335616</v>
+        <v>0.848923064671019</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.274261603375527</v>
+        <v>5.071405387861084</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07753696412517223</v>
+        <v>0.07730634875175299</v>
       </c>
       <c r="C28">
-        <v>243.8012804917997</v>
+        <v>243.3127606642789</v>
       </c>
       <c r="D28">
-        <v>313.6052804917997</v>
+        <v>315.9007606642789</v>
       </c>
       <c r="E28">
-        <v>43.684</v>
+        <v>46.46799999999999</v>
       </c>
       <c r="F28">
-        <v>72.384</v>
+        <v>75.16799999999999</v>
       </c>
       <c r="G28">
         <v>2.58</v>
@@ -3583,28 +3583,28 @@
         <v>20.3</v>
       </c>
       <c r="M28">
-        <v>4.0028352</v>
+        <v>4.156790399999999</v>
       </c>
       <c r="N28">
-        <v>16.2971648</v>
+        <v>16.1432096</v>
       </c>
       <c r="O28">
-        <v>5.70400768</v>
+        <v>5.65012336</v>
       </c>
       <c r="P28">
-        <v>10.59315712</v>
+        <v>10.49308624</v>
       </c>
       <c r="Q28">
-        <v>19.79315712</v>
+        <v>19.69308624</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09215035692590842</v>
+        <v>0.09260438185171641</v>
       </c>
       <c r="T28">
-        <v>0.848923064671019</v>
+        <v>0.8572386906341602</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.071405387861084</v>
+        <v>4.883575558681045</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07730634875175299</v>
+        <v>0.07707573337833373</v>
       </c>
       <c r="C29">
-        <v>243.3127606642789</v>
+        <v>242.858092833816</v>
       </c>
       <c r="D29">
-        <v>315.9007606642789</v>
+        <v>318.2300928338161</v>
       </c>
       <c r="E29">
-        <v>46.46799999999999</v>
+        <v>49.252</v>
       </c>
       <c r="F29">
-        <v>75.16799999999999</v>
+        <v>77.952</v>
       </c>
       <c r="G29">
         <v>2.58</v>
@@ -3665,28 +3665,28 @@
         <v>20.3</v>
       </c>
       <c r="M29">
-        <v>4.156790399999999</v>
+        <v>4.3107456</v>
       </c>
       <c r="N29">
-        <v>16.1432096</v>
+        <v>15.9892544</v>
       </c>
       <c r="O29">
-        <v>5.65012336</v>
+        <v>5.596239039999999</v>
       </c>
       <c r="P29">
-        <v>10.49308624</v>
+        <v>10.39301536</v>
       </c>
       <c r="Q29">
-        <v>19.69308624</v>
+        <v>19.59301536</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09260438185171641</v>
+        <v>0.09307101858101906</v>
       </c>
       <c r="T29">
-        <v>0.8572386906341602</v>
+        <v>0.8657853062073887</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.883575558681045</v>
+        <v>4.709162145871007</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07707573337833373</v>
+        <v>0.07684511800491448</v>
       </c>
       <c r="C30">
-        <v>242.858092833816</v>
+        <v>242.4380313983432</v>
       </c>
       <c r="D30">
-        <v>318.2300928338161</v>
+        <v>320.5940313983432</v>
       </c>
       <c r="E30">
-        <v>49.252</v>
+        <v>52.036</v>
       </c>
       <c r="F30">
-        <v>77.952</v>
+        <v>80.736</v>
       </c>
       <c r="G30">
         <v>2.58</v>
@@ -3747,28 +3747,28 @@
         <v>20.3</v>
       </c>
       <c r="M30">
-        <v>4.3107456</v>
+        <v>4.4647008</v>
       </c>
       <c r="N30">
-        <v>15.9892544</v>
+        <v>15.8352992</v>
       </c>
       <c r="O30">
-        <v>5.596239039999999</v>
+        <v>5.542354720000001</v>
       </c>
       <c r="P30">
-        <v>10.39301536</v>
+        <v>10.29294448</v>
       </c>
       <c r="Q30">
-        <v>19.59301536</v>
+        <v>19.49294448</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09307101858101906</v>
+        <v>0.09355080000692179</v>
       </c>
       <c r="T30">
-        <v>0.8657853062073887</v>
+        <v>0.8745726715150743</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.709162145871007</v>
+        <v>4.546777244289248</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07684511800491448</v>
+        <v>0.07710200263149521</v>
       </c>
       <c r="C31">
-        <v>242.4380313983432</v>
+        <v>237.0230279124222</v>
       </c>
       <c r="D31">
-        <v>320.5940313983432</v>
+        <v>317.9630279124222</v>
       </c>
       <c r="E31">
-        <v>52.03599999999999</v>
+        <v>54.81999999999999</v>
       </c>
       <c r="F31">
-        <v>80.73599999999999</v>
+        <v>83.52</v>
       </c>
       <c r="G31">
         <v>2.58</v>
@@ -3829,45 +3829,45 @@
         <v>20.3</v>
       </c>
       <c r="M31">
-        <v>4.464700799999999</v>
+        <v>4.827456</v>
       </c>
       <c r="N31">
-        <v>15.8352992</v>
+        <v>15.472544</v>
       </c>
       <c r="O31">
-        <v>5.542354720000001</v>
+        <v>5.4153904</v>
       </c>
       <c r="P31">
-        <v>10.29294448</v>
+        <v>10.0571536</v>
       </c>
       <c r="Q31">
-        <v>19.49294448</v>
+        <v>19.2571536</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09355080000692179</v>
+        <v>0.09404428947356458</v>
       </c>
       <c r="T31">
-        <v>0.8745726715150743</v>
+        <v>0.8836111044029795</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.35</v>
       </c>
       <c r="W31">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.546777244289249</v>
+        <v>4.205113417916186</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07710200263149521</v>
+        <v>0.07688763725807594</v>
       </c>
       <c r="C32">
-        <v>237.0230279124222</v>
+        <v>236.431547808551</v>
       </c>
       <c r="D32">
-        <v>317.9630279124222</v>
+        <v>320.155547808551</v>
       </c>
       <c r="E32">
-        <v>54.81999999999999</v>
+        <v>57.60399999999998</v>
       </c>
       <c r="F32">
-        <v>83.52</v>
+        <v>86.30399999999999</v>
       </c>
       <c r="G32">
         <v>2.58</v>
@@ -3911,28 +3911,28 @@
         <v>20.3</v>
       </c>
       <c r="M32">
-        <v>4.827456</v>
+        <v>4.9883712</v>
       </c>
       <c r="N32">
-        <v>15.472544</v>
+        <v>15.3116288</v>
       </c>
       <c r="O32">
-        <v>5.4153904</v>
+        <v>5.35907008</v>
       </c>
       <c r="P32">
-        <v>10.0571536</v>
+        <v>9.952558720000001</v>
       </c>
       <c r="Q32">
-        <v>19.2571536</v>
+        <v>19.15255872</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09404428947356458</v>
+        <v>0.09455208298271878</v>
       </c>
       <c r="T32">
-        <v>0.8836111044029795</v>
+        <v>0.8929115208528531</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.205113417916186</v>
+        <v>4.069464597983407</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07688763725807594</v>
+        <v>0.07740127188465669</v>
       </c>
       <c r="C33">
-        <v>236.431547808551</v>
+        <v>228.4438656325104</v>
       </c>
       <c r="D33">
-        <v>320.155547808551</v>
+        <v>314.9518656325104</v>
       </c>
       <c r="E33">
-        <v>57.60399999999998</v>
+        <v>60.38799999999999</v>
       </c>
       <c r="F33">
-        <v>86.30399999999999</v>
+        <v>89.08799999999999</v>
       </c>
       <c r="G33">
         <v>2.58</v>
@@ -3993,45 +3993,45 @@
         <v>20.3</v>
       </c>
       <c r="M33">
-        <v>4.9883712</v>
+        <v>5.461094399999999</v>
       </c>
       <c r="N33">
-        <v>15.3116288</v>
+        <v>14.8389056</v>
       </c>
       <c r="O33">
-        <v>5.35907008</v>
+        <v>5.19361696</v>
       </c>
       <c r="P33">
-        <v>9.952558720000001</v>
+        <v>9.64528864</v>
       </c>
       <c r="Q33">
-        <v>19.15255872</v>
+        <v>18.84528864</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09455208298271878</v>
+        <v>0.09507481159508338</v>
       </c>
       <c r="T33">
-        <v>0.8929115208528531</v>
+        <v>0.9024854789630169</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.35</v>
       </c>
       <c r="W33">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.069464597983407</v>
+        <v>3.717203643284394</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07740127188465669</v>
+        <v>0.07720965651123744</v>
       </c>
       <c r="C34">
-        <v>228.4438656325104</v>
+        <v>227.5812371483266</v>
       </c>
       <c r="D34">
-        <v>314.9518656325104</v>
+        <v>316.8732371483266</v>
       </c>
       <c r="E34">
-        <v>60.38799999999999</v>
+        <v>63.172</v>
       </c>
       <c r="F34">
-        <v>89.08799999999999</v>
+        <v>91.872</v>
       </c>
       <c r="G34">
         <v>2.58</v>
@@ -4075,28 +4075,28 @@
         <v>20.3</v>
       </c>
       <c r="M34">
-        <v>5.461094399999999</v>
+        <v>5.6317536</v>
       </c>
       <c r="N34">
-        <v>14.8389056</v>
+        <v>14.6682464</v>
       </c>
       <c r="O34">
-        <v>5.19361696</v>
+        <v>5.13388624</v>
       </c>
       <c r="P34">
-        <v>9.64528864</v>
+        <v>9.534360160000002</v>
       </c>
       <c r="Q34">
-        <v>18.84528864</v>
+        <v>18.73436016</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09507481159508338</v>
+        <v>0.09561314404662305</v>
       </c>
       <c r="T34">
-        <v>0.9024854789630169</v>
+        <v>0.9123452268675141</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.717203643284394</v>
+        <v>3.604561108639412</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07720965651123744</v>
+        <v>0.07763684113781819</v>
       </c>
       <c r="C35">
-        <v>227.5812371483266</v>
+        <v>220.5454530313451</v>
       </c>
       <c r="D35">
-        <v>316.8732371483266</v>
+        <v>312.6214530313451</v>
       </c>
       <c r="E35">
-        <v>63.172</v>
+        <v>65.956</v>
       </c>
       <c r="F35">
-        <v>91.872</v>
+        <v>94.65600000000001</v>
       </c>
       <c r="G35">
         <v>2.58</v>
@@ -4157,45 +4157,45 @@
         <v>20.3</v>
       </c>
       <c r="M35">
-        <v>5.6317536</v>
+        <v>6.067449600000001</v>
       </c>
       <c r="N35">
-        <v>14.6682464</v>
+        <v>14.2325504</v>
       </c>
       <c r="O35">
-        <v>5.13388624</v>
+        <v>4.98139264</v>
       </c>
       <c r="P35">
-        <v>9.534360160000002</v>
+        <v>9.251157760000002</v>
       </c>
       <c r="Q35">
-        <v>18.73436016</v>
+        <v>18.45115776</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09561314404662305</v>
+        <v>0.09616778960275484</v>
       </c>
       <c r="T35">
-        <v>0.9123452268675141</v>
+        <v>0.9225037550115415</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0.35</v>
       </c>
       <c r="W35">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.604561108639412</v>
+        <v>3.345722064176685</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07763684113781819</v>
+        <v>0.07746342576439894</v>
       </c>
       <c r="C36">
-        <v>220.5454530313451</v>
+        <v>219.4736292948893</v>
       </c>
       <c r="D36">
-        <v>312.6214530313451</v>
+        <v>314.3336292948894</v>
       </c>
       <c r="E36">
-        <v>65.956</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="F36">
-        <v>94.65600000000001</v>
+        <v>97.44</v>
       </c>
       <c r="G36">
         <v>2.58</v>
@@ -4239,28 +4239,28 @@
         <v>20.3</v>
       </c>
       <c r="M36">
-        <v>6.067449600000001</v>
+        <v>6.245904</v>
       </c>
       <c r="N36">
-        <v>14.2325504</v>
+        <v>14.054096</v>
       </c>
       <c r="O36">
-        <v>4.98139264</v>
+        <v>4.9189336</v>
       </c>
       <c r="P36">
-        <v>9.251157760000002</v>
+        <v>9.135162400000002</v>
       </c>
       <c r="Q36">
-        <v>18.45115776</v>
+        <v>18.3351624</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09616778960275484</v>
+        <v>0.09673950117599836</v>
       </c>
       <c r="T36">
-        <v>0.9225037550115415</v>
+        <v>0.9329748532523081</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.345722064176685</v>
+        <v>3.250130005200208</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07746342576439894</v>
+        <v>0.07729001039097969</v>
       </c>
       <c r="C37">
-        <v>219.4736292948893</v>
+        <v>218.4206634554248</v>
       </c>
       <c r="D37">
-        <v>314.3336292948894</v>
+        <v>316.0646634554248</v>
       </c>
       <c r="E37">
-        <v>68.73999999999999</v>
+        <v>71.524</v>
       </c>
       <c r="F37">
-        <v>97.44</v>
+        <v>100.224</v>
       </c>
       <c r="G37">
         <v>2.58</v>
@@ -4321,28 +4321,28 @@
         <v>20.3</v>
       </c>
       <c r="M37">
-        <v>6.245904</v>
+        <v>6.424358400000001</v>
       </c>
       <c r="N37">
-        <v>14.054096</v>
+        <v>13.8756416</v>
       </c>
       <c r="O37">
-        <v>4.9189336</v>
+        <v>4.85647456</v>
       </c>
       <c r="P37">
-        <v>9.135162400000002</v>
+        <v>9.019167039999999</v>
       </c>
       <c r="Q37">
-        <v>18.3351624</v>
+        <v>18.21916704</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09673950117599836</v>
+        <v>0.09732907873590575</v>
       </c>
       <c r="T37">
-        <v>0.9329748532523081</v>
+        <v>0.9437731733130986</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.250130005200208</v>
+        <v>3.159848616166868</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07729001039097969</v>
+        <v>0.07711659501756042</v>
       </c>
       <c r="C38">
-        <v>218.4206634554248</v>
+        <v>217.3868687892748</v>
       </c>
       <c r="D38">
-        <v>316.0646634554248</v>
+        <v>317.8148687892748</v>
       </c>
       <c r="E38">
-        <v>71.52399999999999</v>
+        <v>74.30799999999999</v>
       </c>
       <c r="F38">
-        <v>100.224</v>
+        <v>103.008</v>
       </c>
       <c r="G38">
         <v>2.58</v>
@@ -4403,28 +4403,28 @@
         <v>20.3</v>
       </c>
       <c r="M38">
-        <v>6.4243584</v>
+        <v>6.6028128</v>
       </c>
       <c r="N38">
-        <v>13.8756416</v>
+        <v>13.6971872</v>
       </c>
       <c r="O38">
-        <v>4.856474560000001</v>
+        <v>4.79401552</v>
       </c>
       <c r="P38">
-        <v>9.019167040000001</v>
+        <v>8.903171680000002</v>
       </c>
       <c r="Q38">
-        <v>18.21916704</v>
+        <v>18.10317168</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09732907873590575</v>
+        <v>0.09793737304374669</v>
       </c>
       <c r="T38">
-        <v>0.9437731733130986</v>
+        <v>0.9549142971853428</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.159848616166869</v>
+        <v>3.074447302216413</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07711659501756042</v>
+        <v>0.07886977964414117</v>
       </c>
       <c r="C39">
-        <v>217.3868687892748</v>
+        <v>197.7540071380649</v>
       </c>
       <c r="D39">
-        <v>317.8148687892748</v>
+        <v>300.9660071380649</v>
       </c>
       <c r="E39">
-        <v>74.30799999999999</v>
+        <v>77.09199999999998</v>
       </c>
       <c r="F39">
-        <v>103.008</v>
+        <v>105.792</v>
       </c>
       <c r="G39">
         <v>2.58</v>
@@ -4485,45 +4485,45 @@
         <v>20.3</v>
       </c>
       <c r="M39">
-        <v>6.6028128</v>
+        <v>7.606444799999999</v>
       </c>
       <c r="N39">
-        <v>13.6971872</v>
+        <v>12.6935552</v>
       </c>
       <c r="O39">
-        <v>4.79401552</v>
+        <v>4.44274432</v>
       </c>
       <c r="P39">
-        <v>8.903171680000002</v>
+        <v>8.250810880000003</v>
       </c>
       <c r="Q39">
-        <v>18.10317168</v>
+        <v>17.45081088</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09793737304374669</v>
+        <v>0.09856528974861478</v>
       </c>
       <c r="T39">
-        <v>0.9549142971853428</v>
+        <v>0.9664148121502402</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V39">
         <v>0.35</v>
       </c>
       <c r="W39">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.074447302216413</v>
+        <v>2.668789498084572</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07886977964414117</v>
+        <v>0.07874706427072192</v>
       </c>
       <c r="C40">
-        <v>197.7540071380649</v>
+        <v>196.0909918682663</v>
       </c>
       <c r="D40">
-        <v>300.9660071380649</v>
+        <v>302.0869918682664</v>
       </c>
       <c r="E40">
-        <v>77.09199999999998</v>
+        <v>79.87599999999999</v>
       </c>
       <c r="F40">
-        <v>105.792</v>
+        <v>108.576</v>
       </c>
       <c r="G40">
         <v>2.58</v>
@@ -4567,28 +4567,28 @@
         <v>20.3</v>
       </c>
       <c r="M40">
-        <v>7.606444799999999</v>
+        <v>7.8066144</v>
       </c>
       <c r="N40">
-        <v>12.6935552</v>
+        <v>12.4933856</v>
       </c>
       <c r="O40">
-        <v>4.44274432</v>
+        <v>4.37268496</v>
       </c>
       <c r="P40">
-        <v>8.250810880000003</v>
+        <v>8.120700639999999</v>
       </c>
       <c r="Q40">
-        <v>17.45081088</v>
+        <v>17.32070064</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09856528974861478</v>
+        <v>0.09921379388642937</v>
       </c>
       <c r="T40">
-        <v>0.9664148121502402</v>
+        <v>0.9782923931795605</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.668789498084572</v>
+        <v>2.600358998133685</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07874706427072192</v>
+        <v>0.07862434889730266</v>
       </c>
       <c r="C41">
-        <v>196.0909918682663</v>
+        <v>194.4363583068269</v>
       </c>
       <c r="D41">
-        <v>302.0869918682664</v>
+        <v>303.2163583068269</v>
       </c>
       <c r="E41">
-        <v>79.87599999999999</v>
+        <v>82.66</v>
       </c>
       <c r="F41">
-        <v>108.576</v>
+        <v>111.36</v>
       </c>
       <c r="G41">
         <v>2.58</v>
@@ -4649,28 +4649,28 @@
         <v>20.3</v>
       </c>
       <c r="M41">
-        <v>7.8066144</v>
+        <v>8.006784000000001</v>
       </c>
       <c r="N41">
-        <v>12.4933856</v>
+        <v>12.293216</v>
       </c>
       <c r="O41">
-        <v>4.37268496</v>
+        <v>4.3026256</v>
       </c>
       <c r="P41">
-        <v>8.120700639999999</v>
+        <v>7.990590399999999</v>
       </c>
       <c r="Q41">
-        <v>17.32070064</v>
+        <v>17.1905904</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09921379388642937</v>
+        <v>0.09988391482883777</v>
       </c>
       <c r="T41">
-        <v>0.9782923931795605</v>
+        <v>0.9905658935765246</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.600358998133685</v>
+        <v>2.535350023180343</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07862434889730266</v>
+        <v>0.0795409835238834</v>
       </c>
       <c r="C42">
-        <v>194.4363583068269</v>
+        <v>183.414939466531</v>
       </c>
       <c r="D42">
-        <v>303.2163583068269</v>
+        <v>294.978939466531</v>
       </c>
       <c r="E42">
-        <v>82.66</v>
+        <v>85.444</v>
       </c>
       <c r="F42">
-        <v>111.36</v>
+        <v>114.144</v>
       </c>
       <c r="G42">
         <v>2.58</v>
@@ -4731,45 +4731,45 @@
         <v>20.3</v>
       </c>
       <c r="M42">
-        <v>8.006784000000001</v>
+        <v>8.652115200000001</v>
       </c>
       <c r="N42">
-        <v>12.293216</v>
+        <v>11.6478848</v>
       </c>
       <c r="O42">
-        <v>4.3026256</v>
+        <v>4.076759679999999</v>
       </c>
       <c r="P42">
-        <v>7.990590399999999</v>
+        <v>7.57112512</v>
       </c>
       <c r="Q42">
-        <v>17.1905904</v>
+        <v>16.77112512</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09988391482883777</v>
+        <v>0.1005767517353956</v>
       </c>
       <c r="T42">
-        <v>0.9905658935765246</v>
+        <v>1.003255444834403</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.35</v>
       </c>
       <c r="W42">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.535350023180343</v>
+        <v>2.346247077246498</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0795409835238834</v>
+        <v>0.07944361815046415</v>
       </c>
       <c r="C43">
-        <v>183.414939466531</v>
+        <v>181.484615027332</v>
       </c>
       <c r="D43">
-        <v>294.978939466531</v>
+        <v>295.8326150273321</v>
       </c>
       <c r="E43">
-        <v>85.444</v>
+        <v>88.22799999999999</v>
       </c>
       <c r="F43">
-        <v>114.144</v>
+        <v>116.928</v>
       </c>
       <c r="G43">
         <v>2.58</v>
@@ -4813,28 +4813,28 @@
         <v>20.3</v>
       </c>
       <c r="M43">
-        <v>8.652115200000001</v>
+        <v>8.863142400000001</v>
       </c>
       <c r="N43">
-        <v>11.6478848</v>
+        <v>11.4368576</v>
       </c>
       <c r="O43">
-        <v>4.076759679999999</v>
+        <v>4.002900159999999</v>
       </c>
       <c r="P43">
-        <v>7.57112512</v>
+        <v>7.43395744</v>
       </c>
       <c r="Q43">
-        <v>16.77112512</v>
+        <v>16.63395744</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1005767517353956</v>
+        <v>0.1012934795697658</v>
       </c>
       <c r="T43">
-        <v>1.003255444834403</v>
+        <v>1.016382566825311</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.346247077246498</v>
+        <v>2.290384051597772</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07944361815046416</v>
+        <v>0.07934625277704491</v>
       </c>
       <c r="C44">
-        <v>181.4846150273319</v>
+        <v>179.5592460411494</v>
       </c>
       <c r="D44">
-        <v>295.8326150273319</v>
+        <v>296.6912460411494</v>
       </c>
       <c r="E44">
-        <v>88.22799999999998</v>
+        <v>91.01199999999999</v>
       </c>
       <c r="F44">
-        <v>116.928</v>
+        <v>119.712</v>
       </c>
       <c r="G44">
         <v>2.58</v>
@@ -4895,28 +4895,28 @@
         <v>20.3</v>
       </c>
       <c r="M44">
-        <v>8.863142399999999</v>
+        <v>9.074169599999999</v>
       </c>
       <c r="N44">
-        <v>11.4368576</v>
+        <v>11.2258304</v>
       </c>
       <c r="O44">
-        <v>4.00290016</v>
+        <v>3.92904064</v>
       </c>
       <c r="P44">
-        <v>7.433957440000001</v>
+        <v>7.296789760000001</v>
       </c>
       <c r="Q44">
-        <v>16.63395744</v>
+        <v>16.49678976</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1012934795697658</v>
+        <v>0.1020353557492016</v>
       </c>
       <c r="T44">
-        <v>1.016382566825311</v>
+        <v>1.029970289587831</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.290384051597772</v>
+        <v>2.237119306211778</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07934625277704491</v>
+        <v>0.07924888740362565</v>
       </c>
       <c r="C45">
-        <v>179.5592460411494</v>
+        <v>177.6388757820266</v>
       </c>
       <c r="D45">
-        <v>296.6912460411494</v>
+        <v>297.5548757820266</v>
       </c>
       <c r="E45">
-        <v>91.01199999999999</v>
+        <v>93.79599999999999</v>
       </c>
       <c r="F45">
-        <v>119.712</v>
+        <v>122.496</v>
       </c>
       <c r="G45">
         <v>2.58</v>
@@ -4977,28 +4977,28 @@
         <v>20.3</v>
       </c>
       <c r="M45">
-        <v>9.074169599999999</v>
+        <v>9.2851968</v>
       </c>
       <c r="N45">
-        <v>11.2258304</v>
+        <v>11.0148032</v>
       </c>
       <c r="O45">
-        <v>3.92904064</v>
+        <v>3.85518112</v>
       </c>
       <c r="P45">
-        <v>7.296789760000001</v>
+        <v>7.159622080000001</v>
       </c>
       <c r="Q45">
-        <v>16.49678976</v>
+        <v>16.35962208</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1020353557492016</v>
+        <v>0.1028037275064743</v>
       </c>
       <c r="T45">
-        <v>1.029970289587831</v>
+        <v>1.044043288163297</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.237119306211778</v>
+        <v>2.186275685616055</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07924888740362565</v>
+        <v>0.07915152203020638</v>
       </c>
       <c r="C46">
-        <v>177.6388757820266</v>
+        <v>175.7235480293382</v>
       </c>
       <c r="D46">
-        <v>297.5548757820266</v>
+        <v>298.4235480293382</v>
       </c>
       <c r="E46">
-        <v>93.79599999999999</v>
+        <v>96.57999999999998</v>
       </c>
       <c r="F46">
-        <v>122.496</v>
+        <v>125.28</v>
       </c>
       <c r="G46">
         <v>2.58</v>
@@ -5059,28 +5059,28 @@
         <v>20.3</v>
       </c>
       <c r="M46">
-        <v>9.2851968</v>
+        <v>9.496224</v>
       </c>
       <c r="N46">
-        <v>11.0148032</v>
+        <v>10.803776</v>
       </c>
       <c r="O46">
-        <v>3.85518112</v>
+        <v>3.7813216</v>
       </c>
       <c r="P46">
-        <v>7.159622080000001</v>
+        <v>7.022454400000001</v>
       </c>
       <c r="Q46">
-        <v>16.35962208</v>
+        <v>16.2224544</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1028037275064743</v>
+        <v>0.1036000400549207</v>
       </c>
       <c r="T46">
-        <v>1.044043288163297</v>
+        <v>1.058628032141508</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.186275685616055</v>
+        <v>2.137691781491254</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07915152203020638</v>
+        <v>0.07905415665678714</v>
       </c>
       <c r="C47">
-        <v>175.7235480293382</v>
+        <v>173.8133070751879</v>
       </c>
       <c r="D47">
-        <v>298.4235480293382</v>
+        <v>299.2973070751879</v>
       </c>
       <c r="E47">
-        <v>96.57999999999998</v>
+        <v>99.36399999999999</v>
       </c>
       <c r="F47">
-        <v>125.28</v>
+        <v>128.064</v>
       </c>
       <c r="G47">
         <v>2.58</v>
@@ -5141,28 +5141,28 @@
         <v>20.3</v>
       </c>
       <c r="M47">
-        <v>9.496224</v>
+        <v>9.7072512</v>
       </c>
       <c r="N47">
-        <v>10.803776</v>
+        <v>10.5927488</v>
       </c>
       <c r="O47">
-        <v>3.7813216</v>
+        <v>3.70746208</v>
       </c>
       <c r="P47">
-        <v>7.022454400000001</v>
+        <v>6.885286720000001</v>
       </c>
       <c r="Q47">
-        <v>16.2224544</v>
+        <v>16.08528672</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1036000400549207</v>
+        <v>0.1044258456607169</v>
       </c>
       <c r="T47">
-        <v>1.058628032141508</v>
+        <v>1.073752951822615</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.137691781491254</v>
+        <v>2.091220221024053</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07905415665678714</v>
+        <v>0.07895679128336787</v>
       </c>
       <c r="C48">
-        <v>173.8133070751879</v>
+        <v>171.9081977319377</v>
       </c>
       <c r="D48">
-        <v>299.2973070751879</v>
+        <v>300.1761977319377</v>
       </c>
       <c r="E48">
-        <v>99.36399999999999</v>
+        <v>102.148</v>
       </c>
       <c r="F48">
-        <v>128.064</v>
+        <v>130.848</v>
       </c>
       <c r="G48">
         <v>2.58</v>
@@ -5223,28 +5223,28 @@
         <v>20.3</v>
       </c>
       <c r="M48">
-        <v>9.7072512</v>
+        <v>9.9182784</v>
       </c>
       <c r="N48">
-        <v>10.5927488</v>
+        <v>10.3817216</v>
       </c>
       <c r="O48">
-        <v>3.70746208</v>
+        <v>3.63360256</v>
       </c>
       <c r="P48">
-        <v>6.885286720000001</v>
+        <v>6.748119040000001</v>
       </c>
       <c r="Q48">
-        <v>16.08528672</v>
+        <v>15.94811904</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1044258456607169</v>
+        <v>0.1052828137422035</v>
       </c>
       <c r="T48">
-        <v>1.073752951822615</v>
+        <v>1.089448623189802</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.091220221024053</v>
+        <v>2.046726173768222</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07895679128336787</v>
+        <v>0.07885942590994863</v>
       </c>
       <c r="C49">
-        <v>171.9081977319377</v>
+        <v>170.0082653398674</v>
       </c>
       <c r="D49">
-        <v>300.1761977319377</v>
+        <v>301.0602653398674</v>
       </c>
       <c r="E49">
-        <v>102.148</v>
+        <v>104.932</v>
       </c>
       <c r="F49">
-        <v>130.848</v>
+        <v>133.632</v>
       </c>
       <c r="G49">
         <v>2.58</v>
@@ -5305,28 +5305,28 @@
         <v>20.3</v>
       </c>
       <c r="M49">
-        <v>9.9182784</v>
+        <v>10.1293056</v>
       </c>
       <c r="N49">
-        <v>10.3817216</v>
+        <v>10.1706944</v>
       </c>
       <c r="O49">
-        <v>3.63360256</v>
+        <v>3.55974304</v>
       </c>
       <c r="P49">
-        <v>6.748119040000001</v>
+        <v>6.61095136</v>
       </c>
       <c r="Q49">
-        <v>15.94811904</v>
+        <v>15.81095136</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1052828137422035</v>
+        <v>0.1061727421345166</v>
       </c>
       <c r="T49">
-        <v>1.089448623189802</v>
+        <v>1.105747974224958</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.046726173768222</v>
+        <v>2.004086045148051</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07885942590994863</v>
+        <v>0.08328476053652936</v>
       </c>
       <c r="C50">
-        <v>170.0082653398674</v>
+        <v>131.6820236974868</v>
       </c>
       <c r="D50">
-        <v>301.0602653398674</v>
+        <v>265.5180236974869</v>
       </c>
       <c r="E50">
-        <v>104.932</v>
+        <v>107.716</v>
       </c>
       <c r="F50">
-        <v>133.632</v>
+        <v>136.416</v>
       </c>
       <c r="G50">
         <v>2.58</v>
@@ -5387,45 +5387,45 @@
         <v>20.3</v>
       </c>
       <c r="M50">
-        <v>10.1293056</v>
+        <v>12.27744</v>
       </c>
       <c r="N50">
-        <v>10.1706944</v>
+        <v>8.022560000000002</v>
       </c>
       <c r="O50">
-        <v>3.55974304</v>
+        <v>2.807896</v>
       </c>
       <c r="P50">
-        <v>6.610951360000001</v>
+        <v>5.214664000000002</v>
       </c>
       <c r="Q50">
-        <v>15.81095136</v>
+        <v>14.414664</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1061727421345166</v>
+        <v>0.1070975696794693</v>
       </c>
       <c r="T50">
-        <v>1.105747974224958</v>
+        <v>1.122686515496786</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.35</v>
       </c>
       <c r="W50">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.004086045148051</v>
+        <v>1.653439153439154</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08328476053652936</v>
+        <v>0.08327969516311011</v>
       </c>
       <c r="C51">
-        <v>131.6820236974868</v>
+        <v>128.9339084060928</v>
       </c>
       <c r="D51">
-        <v>265.5180236974869</v>
+        <v>265.5539084060928</v>
       </c>
       <c r="E51">
-        <v>107.716</v>
+        <v>110.5</v>
       </c>
       <c r="F51">
-        <v>136.416</v>
+        <v>139.2</v>
       </c>
       <c r="G51">
         <v>2.58</v>
@@ -5469,28 +5469,28 @@
         <v>20.3</v>
       </c>
       <c r="M51">
-        <v>12.27744</v>
+        <v>12.528</v>
       </c>
       <c r="N51">
-        <v>8.022560000000002</v>
+        <v>7.772000000000002</v>
       </c>
       <c r="O51">
-        <v>2.807896</v>
+        <v>2.720200000000001</v>
       </c>
       <c r="P51">
-        <v>5.214664000000002</v>
+        <v>5.051800000000002</v>
       </c>
       <c r="Q51">
-        <v>14.414664</v>
+        <v>14.2518</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1070975696794693</v>
+        <v>0.1080593903262202</v>
       </c>
       <c r="T51">
-        <v>1.122686515496786</v>
+        <v>1.140302598419487</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.653439153439154</v>
+        <v>1.620370370370371</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08327969516311011</v>
+        <v>0.08327462978969086</v>
       </c>
       <c r="C52">
-        <v>128.9339084060928</v>
+        <v>126.1858028156325</v>
       </c>
       <c r="D52">
-        <v>265.5539084060928</v>
+        <v>265.5898028156325</v>
       </c>
       <c r="E52">
-        <v>110.5</v>
+        <v>113.284</v>
       </c>
       <c r="F52">
-        <v>139.2</v>
+        <v>141.984</v>
       </c>
       <c r="G52">
         <v>2.58</v>
@@ -5551,28 +5551,28 @@
         <v>20.3</v>
       </c>
       <c r="M52">
-        <v>12.528</v>
+        <v>12.77856</v>
       </c>
       <c r="N52">
-        <v>7.772000000000002</v>
+        <v>7.521440000000004</v>
       </c>
       <c r="O52">
-        <v>2.720200000000001</v>
+        <v>2.632504000000001</v>
       </c>
       <c r="P52">
-        <v>5.051800000000002</v>
+        <v>4.888936000000003</v>
       </c>
       <c r="Q52">
-        <v>14.2518</v>
+        <v>14.088936</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1080593903262202</v>
+        <v>0.1090604689585528</v>
       </c>
       <c r="T52">
-        <v>1.140302598419487</v>
+        <v>1.158637705134952</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.620370370370371</v>
+        <v>1.588598402323893</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08327462978969086</v>
+        <v>0.0832695644162716</v>
       </c>
       <c r="C53">
-        <v>126.1858028156325</v>
+        <v>123.4377069300402</v>
       </c>
       <c r="D53">
-        <v>265.5898028156325</v>
+        <v>265.6257069300402</v>
       </c>
       <c r="E53">
-        <v>113.284</v>
+        <v>116.068</v>
       </c>
       <c r="F53">
-        <v>141.984</v>
+        <v>144.768</v>
       </c>
       <c r="G53">
         <v>2.58</v>
@@ -5633,28 +5633,28 @@
         <v>20.3</v>
       </c>
       <c r="M53">
-        <v>12.77856</v>
+        <v>13.02912</v>
       </c>
       <c r="N53">
-        <v>7.521440000000004</v>
+        <v>7.270880000000002</v>
       </c>
       <c r="O53">
-        <v>2.632504000000001</v>
+        <v>2.544808000000001</v>
       </c>
       <c r="P53">
-        <v>4.888936000000003</v>
+        <v>4.726072000000001</v>
       </c>
       <c r="Q53">
-        <v>14.088936</v>
+        <v>13.926072</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1090604689585528</v>
+        <v>0.1101032592005659</v>
       </c>
       <c r="T53">
-        <v>1.158637705134952</v>
+        <v>1.177736774630229</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.588598402323893</v>
+        <v>1.558048433048433</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0832695644162716</v>
+        <v>0.08326449904285235</v>
       </c>
       <c r="C54">
-        <v>123.4377069300402</v>
+        <v>120.6896207532522</v>
       </c>
       <c r="D54">
-        <v>265.6257069300402</v>
+        <v>265.6616207532522</v>
       </c>
       <c r="E54">
-        <v>116.068</v>
+        <v>118.852</v>
       </c>
       <c r="F54">
-        <v>144.768</v>
+        <v>147.552</v>
       </c>
       <c r="G54">
         <v>2.58</v>
@@ -5715,28 +5715,28 @@
         <v>20.3</v>
       </c>
       <c r="M54">
-        <v>13.02912</v>
+        <v>13.27968</v>
       </c>
       <c r="N54">
-        <v>7.270880000000002</v>
+        <v>7.020320000000002</v>
       </c>
       <c r="O54">
-        <v>2.544808000000001</v>
+        <v>2.457112</v>
       </c>
       <c r="P54">
-        <v>4.726072000000001</v>
+        <v>4.563208000000001</v>
       </c>
       <c r="Q54">
-        <v>13.926072</v>
+        <v>13.763208</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1101032592005659</v>
+        <v>0.1111904234954305</v>
       </c>
       <c r="T54">
-        <v>1.177736774630229</v>
+        <v>1.197648570487005</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.558048433048433</v>
+        <v>1.528651292802236</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08326449904285235</v>
+        <v>0.08325943366943309</v>
       </c>
       <c r="C55">
-        <v>120.6896207532522</v>
+        <v>117.9415442892074</v>
       </c>
       <c r="D55">
-        <v>265.6616207532522</v>
+        <v>265.6975442892074</v>
       </c>
       <c r="E55">
-        <v>118.852</v>
+        <v>121.636</v>
       </c>
       <c r="F55">
-        <v>147.552</v>
+        <v>150.336</v>
       </c>
       <c r="G55">
         <v>2.58</v>
@@ -5797,28 +5797,28 @@
         <v>20.3</v>
       </c>
       <c r="M55">
-        <v>13.27968</v>
+        <v>13.53024</v>
       </c>
       <c r="N55">
-        <v>7.020320000000002</v>
+        <v>6.769760000000003</v>
       </c>
       <c r="O55">
-        <v>2.457112</v>
+        <v>2.369416000000001</v>
       </c>
       <c r="P55">
-        <v>4.563208000000001</v>
+        <v>4.400344000000002</v>
       </c>
       <c r="Q55">
-        <v>13.763208</v>
+        <v>13.600344</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1111904234954305</v>
+        <v>0.1123248558031154</v>
       </c>
       <c r="T55">
-        <v>1.197648570487005</v>
+        <v>1.218426096598425</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.528651292802236</v>
+        <v>1.500342935528121</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08325943366943309</v>
+        <v>0.1070023438441859</v>
       </c>
       <c r="C56">
-        <v>117.9415442892074</v>
+        <v>12.08252246044202</v>
       </c>
       <c r="D56">
-        <v>265.6975442892074</v>
+        <v>162.622522460442</v>
       </c>
       <c r="E56">
-        <v>121.636</v>
+        <v>124.42</v>
       </c>
       <c r="F56">
-        <v>150.336</v>
+        <v>153.12</v>
       </c>
       <c r="G56">
         <v>2.58</v>
@@ -5879,45 +5879,45 @@
         <v>20.3</v>
       </c>
       <c r="M56">
-        <v>13.53024</v>
+        <v>22.478016</v>
       </c>
       <c r="N56">
-        <v>6.769760000000003</v>
+        <v>-2.178016000000003</v>
       </c>
       <c r="O56">
-        <v>2.369416000000001</v>
+        <v>-0.762305600000001</v>
       </c>
       <c r="P56">
-        <v>4.400344000000002</v>
+        <v>-1.415710400000002</v>
       </c>
       <c r="Q56">
-        <v>13.600344</v>
+        <v>7.784289599999997</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1123248558031154</v>
+        <v>0.1150737270611539</v>
       </c>
       <c r="T56">
-        <v>1.218426096598425</v>
+        <v>1.268772639053112</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.35</v>
+        <v>0.3160866154735364</v>
       </c>
       <c r="W56">
-        <v>0.0585</v>
+        <v>0.1003984848484849</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.500342935528121</v>
+        <v>0.9031046156386755</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1070023438441859</v>
+        <v>0.1080123438441859</v>
       </c>
       <c r="C57">
-        <v>12.08252246044202</v>
+        <v>6.658391297783822</v>
       </c>
       <c r="D57">
-        <v>162.622522460442</v>
+        <v>159.9823912977838</v>
       </c>
       <c r="E57">
-        <v>124.42</v>
+        <v>127.204</v>
       </c>
       <c r="F57">
-        <v>153.12</v>
+        <v>155.904</v>
       </c>
       <c r="G57">
         <v>2.58</v>
@@ -5961,37 +5961,37 @@
         <v>20.3</v>
       </c>
       <c r="M57">
-        <v>22.478016</v>
+        <v>22.8867072</v>
       </c>
       <c r="N57">
-        <v>-2.178016000000003</v>
+        <v>-2.586707199999999</v>
       </c>
       <c r="O57">
-        <v>-0.762305600000001</v>
+        <v>-0.9053475199999997</v>
       </c>
       <c r="P57">
-        <v>-1.415710400000002</v>
+        <v>-1.681359679999999</v>
       </c>
       <c r="Q57">
-        <v>7.784289599999997</v>
+        <v>7.518640319999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1150737270611539</v>
+        <v>0.1166481299489074</v>
       </c>
       <c r="T57">
-        <v>1.268772639053112</v>
+        <v>1.297608380849773</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.3160866154735364</v>
+        <v>0.3104422116257947</v>
       </c>
       <c r="W57">
-        <v>0.1003984848484849</v>
+        <v>0.1012270833333333</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9031046156386755</v>
+        <v>0.8869777475022707</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1080123438441859</v>
+        <v>0.109022343844186</v>
       </c>
       <c r="C58">
-        <v>6.658391297783822</v>
+        <v>1.318614251475736</v>
       </c>
       <c r="D58">
-        <v>159.9823912977838</v>
+        <v>157.4266142514757</v>
       </c>
       <c r="E58">
-        <v>127.204</v>
+        <v>129.988</v>
       </c>
       <c r="F58">
-        <v>155.904</v>
+        <v>158.688</v>
       </c>
       <c r="G58">
         <v>2.58</v>
@@ -6043,37 +6043,37 @@
         <v>20.3</v>
       </c>
       <c r="M58">
-        <v>22.8867072</v>
+        <v>23.2953984</v>
       </c>
       <c r="N58">
-        <v>-2.586707199999999</v>
+        <v>-2.995398400000003</v>
       </c>
       <c r="O58">
-        <v>-0.9053475199999997</v>
+        <v>-1.048389440000001</v>
       </c>
       <c r="P58">
-        <v>-1.681359679999999</v>
+        <v>-1.947008960000002</v>
       </c>
       <c r="Q58">
-        <v>7.518640319999999</v>
+        <v>7.252991039999998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1166481299489074</v>
+        <v>0.1182957608779518</v>
       </c>
       <c r="T58">
-        <v>1.297608380849773</v>
+        <v>1.327785319939303</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.3104422116257947</v>
+        <v>0.3049958570358685</v>
       </c>
       <c r="W58">
-        <v>0.1012270833333333</v>
+        <v>0.1020266081871345</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8869777475022707</v>
+        <v>0.8714167343881957</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.109022343844186</v>
+        <v>0.1100323438441859</v>
       </c>
       <c r="C59">
-        <v>1.318614251475736</v>
+        <v>-3.940787872720335</v>
       </c>
       <c r="D59">
-        <v>157.4266142514757</v>
+        <v>154.9512121272797</v>
       </c>
       <c r="E59">
-        <v>129.988</v>
+        <v>132.772</v>
       </c>
       <c r="F59">
-        <v>158.688</v>
+        <v>161.472</v>
       </c>
       <c r="G59">
         <v>2.58</v>
@@ -6125,37 +6125,37 @@
         <v>20.3</v>
       </c>
       <c r="M59">
-        <v>23.2953984</v>
+        <v>23.7040896</v>
       </c>
       <c r="N59">
-        <v>-2.995398400000003</v>
+        <v>-3.404089600000002</v>
       </c>
       <c r="O59">
-        <v>-1.048389440000001</v>
+        <v>-1.191431360000001</v>
       </c>
       <c r="P59">
-        <v>-1.947008960000002</v>
+        <v>-2.212658240000001</v>
       </c>
       <c r="Q59">
-        <v>7.252991039999998</v>
+        <v>6.987341759999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1182957608779518</v>
+        <v>0.1200218504226649</v>
       </c>
       <c r="T59">
-        <v>1.327785319939303</v>
+        <v>1.359399256128334</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.3049958570358685</v>
+        <v>0.2997373077766293</v>
       </c>
       <c r="W59">
-        <v>0.1020266081871345</v>
+        <v>0.1027985632183908</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8714167343881957</v>
+        <v>0.8563923079332267</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1100323438441859</v>
+        <v>0.1110423438441859</v>
       </c>
       <c r="C60">
-        <v>-3.940787872720307</v>
+        <v>-9.123547865499091</v>
       </c>
       <c r="D60">
-        <v>154.9512121272797</v>
+        <v>152.5524521345009</v>
       </c>
       <c r="E60">
-        <v>132.772</v>
+        <v>135.556</v>
       </c>
       <c r="F60">
-        <v>161.472</v>
+        <v>164.256</v>
       </c>
       <c r="G60">
         <v>2.58</v>
@@ -6207,37 +6207,37 @@
         <v>20.3</v>
       </c>
       <c r="M60">
-        <v>23.7040896</v>
+        <v>24.1127808</v>
       </c>
       <c r="N60">
-        <v>-3.404089599999999</v>
+        <v>-3.812780799999999</v>
       </c>
       <c r="O60">
-        <v>-1.191431359999999</v>
+        <v>-1.334473279999999</v>
       </c>
       <c r="P60">
-        <v>-2.21265824</v>
+        <v>-2.47830752</v>
       </c>
       <c r="Q60">
-        <v>6.98734176</v>
+        <v>6.72169248</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1200218504226649</v>
+        <v>0.1218321394573641</v>
       </c>
       <c r="T60">
-        <v>1.359399256128334</v>
+        <v>1.392555335546098</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2997373077766294</v>
+        <v>0.2946570144244831</v>
       </c>
       <c r="W60">
-        <v>0.1027985632183908</v>
+        <v>0.1035443502824859</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8563923079332268</v>
+        <v>0.8418771840699518</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1110423438441859</v>
+        <v>0.1120523438441859</v>
       </c>
       <c r="C61">
-        <v>-9.123547865499091</v>
+        <v>-14.23317089580596</v>
       </c>
       <c r="D61">
-        <v>152.5524521345009</v>
+        <v>150.226829104194</v>
       </c>
       <c r="E61">
-        <v>135.556</v>
+        <v>138.34</v>
       </c>
       <c r="F61">
-        <v>164.256</v>
+        <v>167.04</v>
       </c>
       <c r="G61">
         <v>2.58</v>
@@ -6289,37 +6289,37 @@
         <v>20.3</v>
       </c>
       <c r="M61">
-        <v>24.1127808</v>
+        <v>24.521472</v>
       </c>
       <c r="N61">
-        <v>-3.812780799999999</v>
+        <v>-4.221472000000002</v>
       </c>
       <c r="O61">
-        <v>-1.334473279999999</v>
+        <v>-1.477515200000001</v>
       </c>
       <c r="P61">
-        <v>-2.47830752</v>
+        <v>-2.743956800000001</v>
       </c>
       <c r="Q61">
-        <v>6.72169248</v>
+        <v>6.456043199999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1218321394573641</v>
+        <v>0.1237329429437981</v>
       </c>
       <c r="T61">
-        <v>1.392555335546098</v>
+        <v>1.42736921893475</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2946570144244831</v>
+        <v>0.2897460641840751</v>
       </c>
       <c r="W61">
-        <v>0.1035443502824859</v>
+        <v>0.1042652777777778</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8418771840699518</v>
+        <v>0.8278458976687859</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1120523438441859</v>
+        <v>0.1130623438441859</v>
       </c>
       <c r="C62">
-        <v>-14.23317089580596</v>
+        <v>-19.27295160048547</v>
       </c>
       <c r="D62">
-        <v>150.226829104194</v>
+        <v>147.9710483995145</v>
       </c>
       <c r="E62">
-        <v>138.34</v>
+        <v>141.124</v>
       </c>
       <c r="F62">
-        <v>167.04</v>
+        <v>169.824</v>
       </c>
       <c r="G62">
         <v>2.58</v>
@@ -6371,37 +6371,37 @@
         <v>20.3</v>
       </c>
       <c r="M62">
-        <v>24.521472</v>
+        <v>24.9301632</v>
       </c>
       <c r="N62">
-        <v>-4.221472000000002</v>
+        <v>-4.630163199999998</v>
       </c>
       <c r="O62">
-        <v>-1.477515200000001</v>
+        <v>-1.620557119999999</v>
       </c>
       <c r="P62">
-        <v>-2.743956800000001</v>
+        <v>-3.009606079999999</v>
       </c>
       <c r="Q62">
-        <v>6.456043199999998</v>
+        <v>6.19039392</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1237329429437981</v>
+        <v>0.1257312235321007</v>
       </c>
       <c r="T62">
-        <v>1.42736921893475</v>
+        <v>1.463968429676667</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2897460641840751</v>
+        <v>0.2849961287056476</v>
       </c>
       <c r="W62">
-        <v>0.1042652777777778</v>
+        <v>0.1049625683060109</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8278458976687859</v>
+        <v>0.8142746534447076</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1130623438441859</v>
+        <v>0.1140723438441859</v>
       </c>
       <c r="C63">
-        <v>-19.27295160048547</v>
+        <v>-24.24598965701671</v>
       </c>
       <c r="D63">
-        <v>147.9710483995145</v>
+        <v>145.7820103429833</v>
       </c>
       <c r="E63">
-        <v>141.124</v>
+        <v>143.908</v>
       </c>
       <c r="F63">
-        <v>169.824</v>
+        <v>172.608</v>
       </c>
       <c r="G63">
         <v>2.58</v>
@@ -6453,37 +6453,37 @@
         <v>20.3</v>
       </c>
       <c r="M63">
-        <v>24.9301632</v>
+        <v>25.3388544</v>
       </c>
       <c r="N63">
-        <v>-4.630163199999998</v>
+        <v>-5.038854399999998</v>
       </c>
       <c r="O63">
-        <v>-1.620557119999999</v>
+        <v>-1.763599039999999</v>
       </c>
       <c r="P63">
-        <v>-3.009606079999999</v>
+        <v>-3.275255359999999</v>
       </c>
       <c r="Q63">
-        <v>6.19039392</v>
+        <v>5.92474464</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1257312235321007</v>
+        <v>0.1278346767829454</v>
       </c>
       <c r="T63">
-        <v>1.463968429676667</v>
+        <v>1.502493914668158</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2849961287056476</v>
+        <v>0.2803994169523307</v>
       </c>
       <c r="W63">
-        <v>0.1049625683060109</v>
+        <v>0.1056373655913979</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8142746534447076</v>
+        <v>0.8011411912923736</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1140723438441859</v>
+        <v>0.1508664298972432</v>
       </c>
       <c r="C64">
-        <v>-24.24598965701671</v>
+        <v>-78.08260312064553</v>
       </c>
       <c r="D64">
-        <v>145.7820103429833</v>
+        <v>94.72939687935447</v>
       </c>
       <c r="E64">
-        <v>143.908</v>
+        <v>146.692</v>
       </c>
       <c r="F64">
-        <v>172.608</v>
+        <v>175.392</v>
       </c>
       <c r="G64">
         <v>2.58</v>
@@ -6535,45 +6535,45 @@
         <v>20.3</v>
       </c>
       <c r="M64">
-        <v>25.3388544</v>
+        <v>35.2187136</v>
       </c>
       <c r="N64">
-        <v>-5.038854399999998</v>
+        <v>-14.9187136</v>
       </c>
       <c r="O64">
-        <v>-1.763599039999999</v>
+        <v>-5.221549759999999</v>
       </c>
       <c r="P64">
-        <v>-3.275255359999999</v>
+        <v>-9.697163840000002</v>
       </c>
       <c r="Q64">
-        <v>5.92474464</v>
+        <v>-0.4971638400000025</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1278346767829454</v>
+        <v>0.1348196303529095</v>
       </c>
       <c r="T64">
-        <v>1.502493914668158</v>
+        <v>1.630425792316422</v>
       </c>
       <c r="U64">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.2803994169523307</v>
+        <v>0.2017393389405341</v>
       </c>
       <c r="W64">
-        <v>0.1056373655913979</v>
+        <v>0.1602907407407407</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8011411912923736</v>
+        <v>0.576398111258669</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1508664298972432</v>
+        <v>0.1524164298972432</v>
       </c>
       <c r="C65">
-        <v>-78.08260312064553</v>
+        <v>-82.2437882815491</v>
       </c>
       <c r="D65">
-        <v>94.72939687935447</v>
+        <v>93.35221171845089</v>
       </c>
       <c r="E65">
-        <v>146.692</v>
+        <v>149.476</v>
       </c>
       <c r="F65">
-        <v>175.392</v>
+        <v>178.176</v>
       </c>
       <c r="G65">
         <v>2.58</v>
@@ -6617,37 +6617,37 @@
         <v>20.3</v>
       </c>
       <c r="M65">
-        <v>35.2187136</v>
+        <v>35.7777408</v>
       </c>
       <c r="N65">
-        <v>-14.9187136</v>
+        <v>-15.4777408</v>
       </c>
       <c r="O65">
-        <v>-5.221549759999999</v>
+        <v>-5.417209279999998</v>
       </c>
       <c r="P65">
-        <v>-9.697163840000002</v>
+        <v>-10.06053152</v>
       </c>
       <c r="Q65">
-        <v>-0.4971638400000025</v>
+        <v>-0.8605315199999986</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1348196303529095</v>
+        <v>0.1372923978627125</v>
       </c>
       <c r="T65">
-        <v>1.630425792316422</v>
+        <v>1.675715397658544</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.2017393389405341</v>
+        <v>0.1985871617695883</v>
       </c>
       <c r="W65">
-        <v>0.1602907407407407</v>
+        <v>0.1609236979166667</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.576398111258669</v>
+        <v>0.5673918907702524</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1524164298972432</v>
+        <v>0.1539664298972432</v>
       </c>
       <c r="C66">
-        <v>-82.2437882815491</v>
+        <v>-86.36550395082891</v>
       </c>
       <c r="D66">
-        <v>93.35221171845089</v>
+        <v>92.01449604917107</v>
       </c>
       <c r="E66">
-        <v>149.476</v>
+        <v>152.26</v>
       </c>
       <c r="F66">
-        <v>178.176</v>
+        <v>180.96</v>
       </c>
       <c r="G66">
         <v>2.58</v>
@@ -6699,37 +6699,37 @@
         <v>20.3</v>
       </c>
       <c r="M66">
-        <v>35.7777408</v>
+        <v>36.336768</v>
       </c>
       <c r="N66">
-        <v>-15.4777408</v>
+        <v>-16.036768</v>
       </c>
       <c r="O66">
-        <v>-5.417209279999998</v>
+        <v>-5.612868799999999</v>
       </c>
       <c r="P66">
-        <v>-10.06053152</v>
+        <v>-10.4238992</v>
       </c>
       <c r="Q66">
-        <v>-0.8605315199999986</v>
+        <v>-1.2238992</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1372923978627125</v>
+        <v>0.1399064663730757</v>
       </c>
       <c r="T66">
-        <v>1.675715397658544</v>
+        <v>1.723592980448789</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1985871617695883</v>
+        <v>0.1955319746654408</v>
       </c>
       <c r="W66">
-        <v>0.1609236979166667</v>
+        <v>0.1615371794871795</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5673918907702524</v>
+        <v>0.5586627847584023</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1539664298972432</v>
+        <v>0.1555164298972432</v>
       </c>
       <c r="C67">
-        <v>-86.36550395082891</v>
+        <v>-90.44942292385596</v>
       </c>
       <c r="D67">
-        <v>92.01449604917107</v>
+        <v>90.71457707614404</v>
       </c>
       <c r="E67">
-        <v>152.26</v>
+        <v>155.044</v>
       </c>
       <c r="F67">
-        <v>180.96</v>
+        <v>183.744</v>
       </c>
       <c r="G67">
         <v>2.58</v>
@@ -6781,37 +6781,37 @@
         <v>20.3</v>
       </c>
       <c r="M67">
-        <v>36.336768</v>
+        <v>36.8957952</v>
       </c>
       <c r="N67">
-        <v>-16.036768</v>
+        <v>-16.5957952</v>
       </c>
       <c r="O67">
-        <v>-5.612868799999999</v>
+        <v>-5.80852832</v>
       </c>
       <c r="P67">
-        <v>-10.4238992</v>
+        <v>-10.78726688</v>
       </c>
       <c r="Q67">
-        <v>-1.2238992</v>
+        <v>-1.587266880000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1399064663730757</v>
+        <v>0.1426743036193427</v>
       </c>
       <c r="T67">
-        <v>1.723592980448789</v>
+        <v>1.774286891638459</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1955319746654408</v>
+        <v>0.1925693689886917</v>
       </c>
       <c r="W67">
-        <v>0.1615371794871795</v>
+        <v>0.1621320707070707</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5586627847584023</v>
+        <v>0.5501981971105476</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1555164298972432</v>
+        <v>0.1570664298972432</v>
       </c>
       <c r="C68">
-        <v>-90.44942292385596</v>
+        <v>-94.49712478431718</v>
       </c>
       <c r="D68">
-        <v>90.71457707614404</v>
+        <v>89.45087521568281</v>
       </c>
       <c r="E68">
-        <v>155.044</v>
+        <v>157.828</v>
       </c>
       <c r="F68">
-        <v>183.744</v>
+        <v>186.528</v>
       </c>
       <c r="G68">
         <v>2.58</v>
@@ -6863,37 +6863,37 @@
         <v>20.3</v>
       </c>
       <c r="M68">
-        <v>36.8957952</v>
+        <v>37.4548224</v>
       </c>
       <c r="N68">
-        <v>-16.5957952</v>
+        <v>-17.1548224</v>
       </c>
       <c r="O68">
-        <v>-5.80852832</v>
+        <v>-6.004187839999998</v>
       </c>
       <c r="P68">
-        <v>-10.78726688</v>
+        <v>-11.15063456</v>
       </c>
       <c r="Q68">
-        <v>-1.587266880000001</v>
+        <v>-1.950634559999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1426743036193427</v>
+        <v>0.1456098885775046</v>
       </c>
       <c r="T68">
-        <v>1.774286891638459</v>
+        <v>1.828053161082049</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1925693689886917</v>
+        <v>0.1896951993022933</v>
       </c>
       <c r="W68">
-        <v>0.1621320707070707</v>
+        <v>0.1627092039800995</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5501981971105476</v>
+        <v>0.541986283720838</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1570664298972432</v>
+        <v>0.1586164298972432</v>
       </c>
       <c r="C69">
-        <v>-94.49712478431718</v>
+        <v>-98.51010230745446</v>
       </c>
       <c r="D69">
-        <v>89.45087521568281</v>
+        <v>88.22189769254555</v>
       </c>
       <c r="E69">
-        <v>157.828</v>
+        <v>160.612</v>
       </c>
       <c r="F69">
-        <v>186.528</v>
+        <v>189.312</v>
       </c>
       <c r="G69">
         <v>2.58</v>
@@ -6945,37 +6945,37 @@
         <v>20.3</v>
       </c>
       <c r="M69">
-        <v>37.4548224</v>
+        <v>38.0138496</v>
       </c>
       <c r="N69">
-        <v>-17.1548224</v>
+        <v>-17.7138496</v>
       </c>
       <c r="O69">
-        <v>-6.004187839999998</v>
+        <v>-6.19984736</v>
       </c>
       <c r="P69">
-        <v>-11.15063456</v>
+        <v>-11.51400224</v>
       </c>
       <c r="Q69">
-        <v>-1.950634559999999</v>
+        <v>-2.314002240000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1456098885775046</v>
+        <v>0.1487289475955516</v>
       </c>
       <c r="T69">
-        <v>1.828053161082049</v>
+        <v>1.885179822365863</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1896951993022933</v>
+        <v>0.1869055640184361</v>
       </c>
       <c r="W69">
-        <v>0.1627092039800995</v>
+        <v>0.163269362745098</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.541986283720838</v>
+        <v>0.5340158971955316</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1586164298972432</v>
+        <v>0.1601664298972432</v>
       </c>
       <c r="C70">
-        <v>-98.51010230745446</v>
+        <v>-102.4897673426078</v>
       </c>
       <c r="D70">
-        <v>88.22189769254555</v>
+        <v>87.02623265739221</v>
       </c>
       <c r="E70">
-        <v>160.612</v>
+        <v>163.396</v>
       </c>
       <c r="F70">
-        <v>189.312</v>
+        <v>192.096</v>
       </c>
       <c r="G70">
         <v>2.58</v>
@@ -7027,37 +7027,37 @@
         <v>20.3</v>
       </c>
       <c r="M70">
-        <v>38.0138496</v>
+        <v>38.5728768</v>
       </c>
       <c r="N70">
-        <v>-17.7138496</v>
+        <v>-18.2728768</v>
       </c>
       <c r="O70">
-        <v>-6.19984736</v>
+        <v>-6.39550688</v>
       </c>
       <c r="P70">
-        <v>-11.51400224</v>
+        <v>-11.87736992</v>
       </c>
       <c r="Q70">
-        <v>-2.314002240000001</v>
+        <v>-2.677369920000004</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1487289475955516</v>
+        <v>0.1520492362276662</v>
       </c>
       <c r="T70">
-        <v>1.885179822365863</v>
+        <v>1.945992074700245</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1869055640184361</v>
+        <v>0.1841967877283138</v>
       </c>
       <c r="W70">
-        <v>0.163269362745098</v>
+        <v>0.1638132850241546</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5340158971955316</v>
+        <v>0.5262765363666109</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1601664298972432</v>
+        <v>0.1617164298972432</v>
       </c>
       <c r="C71">
-        <v>-102.4897673426078</v>
+        <v>-106.4374562238003</v>
       </c>
       <c r="D71">
-        <v>87.02623265739221</v>
+        <v>85.86254377619966</v>
       </c>
       <c r="E71">
-        <v>163.396</v>
+        <v>166.18</v>
       </c>
       <c r="F71">
-        <v>192.096</v>
+        <v>194.88</v>
       </c>
       <c r="G71">
         <v>2.58</v>
@@ -7109,37 +7109,37 @@
         <v>20.3</v>
       </c>
       <c r="M71">
-        <v>38.5728768</v>
+        <v>39.131904</v>
       </c>
       <c r="N71">
-        <v>-18.2728768</v>
+        <v>-18.831904</v>
       </c>
       <c r="O71">
-        <v>-6.39550688</v>
+        <v>-6.591166399999999</v>
       </c>
       <c r="P71">
-        <v>-11.87736992</v>
+        <v>-12.2407376</v>
       </c>
       <c r="Q71">
-        <v>-2.677369920000004</v>
+        <v>-3.0407376</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1520492362276662</v>
+        <v>0.155590877435255</v>
       </c>
       <c r="T71">
-        <v>1.945992074700245</v>
+        <v>2.010858477190254</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1841967877283138</v>
+        <v>0.1815654050464807</v>
       </c>
       <c r="W71">
-        <v>0.1638132850241546</v>
+        <v>0.1643416666666667</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5262765363666109</v>
+        <v>0.5187583001328022</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1617164298972432</v>
+        <v>0.1632664298972432</v>
       </c>
       <c r="C72">
-        <v>-106.4374562238003</v>
+        <v>-110.3544347519596</v>
       </c>
       <c r="D72">
-        <v>85.86254377619966</v>
+        <v>84.72956524804037</v>
       </c>
       <c r="E72">
-        <v>166.18</v>
+        <v>168.964</v>
       </c>
       <c r="F72">
-        <v>194.88</v>
+        <v>197.664</v>
       </c>
       <c r="G72">
         <v>2.58</v>
@@ -7191,37 +7191,37 @@
         <v>20.3</v>
       </c>
       <c r="M72">
-        <v>39.131904</v>
+        <v>39.6909312</v>
       </c>
       <c r="N72">
-        <v>-18.831904</v>
+        <v>-19.3909312</v>
       </c>
       <c r="O72">
-        <v>-6.591166399999999</v>
+        <v>-6.78682592</v>
       </c>
       <c r="P72">
-        <v>-12.2407376</v>
+        <v>-12.60410528</v>
       </c>
       <c r="Q72">
-        <v>-3.0407376</v>
+        <v>-3.404105280000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.155590877435255</v>
+        <v>0.1593767697606087</v>
       </c>
       <c r="T72">
-        <v>2.010858477190254</v>
+        <v>2.080198424679573</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1815654050464807</v>
+        <v>0.179008145820474</v>
       </c>
       <c r="W72">
-        <v>0.1643416666666667</v>
+        <v>0.1648551643192488</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5187583001328022</v>
+        <v>0.5114518452013542</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1632664298972432</v>
+        <v>0.1648164298972432</v>
       </c>
       <c r="C73">
-        <v>-110.3544347519597</v>
+        <v>-114.2419027878254</v>
       </c>
       <c r="D73">
-        <v>84.72956524804033</v>
+        <v>83.62609721217463</v>
       </c>
       <c r="E73">
-        <v>168.964</v>
+        <v>171.748</v>
       </c>
       <c r="F73">
-        <v>197.664</v>
+        <v>200.448</v>
       </c>
       <c r="G73">
         <v>2.58</v>
@@ -7273,37 +7273,37 @@
         <v>20.3</v>
       </c>
       <c r="M73">
-        <v>39.6909312</v>
+        <v>40.2499584</v>
       </c>
       <c r="N73">
-        <v>-19.3909312</v>
+        <v>-19.9499584</v>
       </c>
       <c r="O73">
-        <v>-6.78682592</v>
+        <v>-6.982485439999999</v>
       </c>
       <c r="P73">
-        <v>-12.60410528</v>
+        <v>-12.96747296</v>
       </c>
       <c r="Q73">
-        <v>-3.404105280000001</v>
+        <v>-3.767472959999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1593767697606087</v>
+        <v>0.1634330829663447</v>
       </c>
       <c r="T73">
-        <v>2.080198424679573</v>
+        <v>2.154491225560986</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.179008145820474</v>
+        <v>0.1765219215729674</v>
       </c>
       <c r="W73">
-        <v>0.1648551643192488</v>
+        <v>0.1653543981481481</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5114518452013542</v>
+        <v>0.5043483473513355</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1648164298972432</v>
+        <v>0.1926282599274483</v>
       </c>
       <c r="C74">
-        <v>-114.2419027878254</v>
+        <v>-132.8661422819367</v>
       </c>
       <c r="D74">
-        <v>83.62609721217463</v>
+        <v>67.78585771806326</v>
       </c>
       <c r="E74">
-        <v>171.748</v>
+        <v>174.532</v>
       </c>
       <c r="F74">
-        <v>200.448</v>
+        <v>203.232</v>
       </c>
       <c r="G74">
         <v>2.58</v>
@@ -7355,45 +7355,45 @@
         <v>20.3</v>
       </c>
       <c r="M74">
-        <v>40.2499584</v>
+        <v>47.92210559999999</v>
       </c>
       <c r="N74">
-        <v>-19.9499584</v>
+        <v>-27.62210559999999</v>
       </c>
       <c r="O74">
-        <v>-6.982485439999999</v>
+        <v>-9.667736959999997</v>
       </c>
       <c r="P74">
-        <v>-12.96747296</v>
+        <v>-17.95436864</v>
       </c>
       <c r="Q74">
-        <v>-3.767472959999999</v>
+        <v>-8.754368639999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1634330829663447</v>
+        <v>0.1704262713362283</v>
       </c>
       <c r="T74">
-        <v>2.154491225560986</v>
+        <v>2.282573926461719</v>
       </c>
       <c r="U74">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1765219215729674</v>
+        <v>0.1482614319851589</v>
       </c>
       <c r="W74">
-        <v>0.1653543981481481</v>
+        <v>0.2008399543378996</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.5043483473513355</v>
+        <v>0.4236040913861682</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1926282599274483</v>
+        <v>0.1945282599274483</v>
       </c>
       <c r="C75">
-        <v>-132.8661422819367</v>
+        <v>-136.5161050097139</v>
       </c>
       <c r="D75">
-        <v>67.78585771806326</v>
+        <v>66.91989499028612</v>
       </c>
       <c r="E75">
-        <v>174.532</v>
+        <v>177.316</v>
       </c>
       <c r="F75">
-        <v>203.232</v>
+        <v>206.016</v>
       </c>
       <c r="G75">
         <v>2.58</v>
@@ -7437,37 +7437,37 @@
         <v>20.3</v>
       </c>
       <c r="M75">
-        <v>47.92210559999999</v>
+        <v>48.5785728</v>
       </c>
       <c r="N75">
-        <v>-27.62210559999999</v>
+        <v>-28.2785728</v>
       </c>
       <c r="O75">
-        <v>-9.667736959999997</v>
+        <v>-9.897500479999998</v>
       </c>
       <c r="P75">
-        <v>-17.95436864</v>
+        <v>-18.38107232</v>
       </c>
       <c r="Q75">
-        <v>-8.754368639999999</v>
+        <v>-9.181072319999998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1704262713362283</v>
+        <v>0.1752195894645448</v>
       </c>
       <c r="T75">
-        <v>2.282573926461719</v>
+        <v>2.370365231325631</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1482614319851589</v>
+        <v>0.1462578991204946</v>
       </c>
       <c r="W75">
-        <v>0.2008399543378996</v>
+        <v>0.2013123873873874</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4236040913861682</v>
+        <v>0.4178797117728416</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1945282599274483</v>
+        <v>0.1964282599274483</v>
       </c>
       <c r="C76">
-        <v>-136.5161050097139</v>
+        <v>-140.1442215157585</v>
       </c>
       <c r="D76">
-        <v>66.91989499028612</v>
+        <v>66.07577848424147</v>
       </c>
       <c r="E76">
-        <v>177.316</v>
+        <v>180.1</v>
       </c>
       <c r="F76">
-        <v>206.016</v>
+        <v>208.8</v>
       </c>
       <c r="G76">
         <v>2.58</v>
@@ -7519,37 +7519,37 @@
         <v>20.3</v>
       </c>
       <c r="M76">
-        <v>48.5785728</v>
+        <v>49.23504</v>
       </c>
       <c r="N76">
-        <v>-28.2785728</v>
+        <v>-28.93504</v>
       </c>
       <c r="O76">
-        <v>-9.897500479999998</v>
+        <v>-10.127264</v>
       </c>
       <c r="P76">
-        <v>-18.38107232</v>
+        <v>-18.807776</v>
       </c>
       <c r="Q76">
-        <v>-9.181072319999998</v>
+        <v>-9.607775999999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1752195894645448</v>
+        <v>0.1803963730431266</v>
       </c>
       <c r="T76">
-        <v>2.370365231325631</v>
+        <v>2.465179840578657</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1462578991204946</v>
+        <v>0.1443077937988879</v>
       </c>
       <c r="W76">
-        <v>0.2013123873873874</v>
+        <v>0.2017722222222222</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4178797117728416</v>
+        <v>0.4123079822825371</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1964282599274483</v>
+        <v>0.1983282599274483</v>
       </c>
       <c r="C77">
-        <v>-140.1442215157585</v>
+        <v>-143.7513081960876</v>
       </c>
       <c r="D77">
-        <v>66.07577848424147</v>
+        <v>65.25269180391236</v>
       </c>
       <c r="E77">
-        <v>180.1</v>
+        <v>182.884</v>
       </c>
       <c r="F77">
-        <v>208.8</v>
+        <v>211.584</v>
       </c>
       <c r="G77">
         <v>2.58</v>
@@ -7601,37 +7601,37 @@
         <v>20.3</v>
       </c>
       <c r="M77">
-        <v>49.23504</v>
+        <v>49.8915072</v>
       </c>
       <c r="N77">
-        <v>-28.93504</v>
+        <v>-29.5915072</v>
       </c>
       <c r="O77">
-        <v>-10.127264</v>
+        <v>-10.35702752</v>
       </c>
       <c r="P77">
-        <v>-18.807776</v>
+        <v>-19.23447968</v>
       </c>
       <c r="Q77">
-        <v>-9.607775999999998</v>
+        <v>-10.03447968</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1803963730431266</v>
+        <v>0.1860045552532569</v>
       </c>
       <c r="T77">
-        <v>2.465179840578657</v>
+        <v>2.567895667269434</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1443077937988879</v>
+        <v>0.1424090070383763</v>
       </c>
       <c r="W77">
-        <v>0.2017722222222222</v>
+        <v>0.2022199561403509</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4123079822825371</v>
+        <v>0.4068828772525036</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1983282599274483</v>
+        <v>0.2002282599274484</v>
       </c>
       <c r="C78">
-        <v>-143.7513081960876</v>
+        <v>-147.3381412687758</v>
       </c>
       <c r="D78">
-        <v>65.25269180391236</v>
+        <v>64.44985873122423</v>
       </c>
       <c r="E78">
-        <v>182.884</v>
+        <v>185.668</v>
       </c>
       <c r="F78">
-        <v>211.584</v>
+        <v>214.368</v>
       </c>
       <c r="G78">
         <v>2.58</v>
@@ -7683,37 +7683,37 @@
         <v>20.3</v>
       </c>
       <c r="M78">
-        <v>49.8915072</v>
+        <v>50.5479744</v>
       </c>
       <c r="N78">
-        <v>-29.5915072</v>
+        <v>-30.2479744</v>
       </c>
       <c r="O78">
-        <v>-10.35702752</v>
+        <v>-10.58679104</v>
       </c>
       <c r="P78">
-        <v>-19.23447968</v>
+        <v>-19.66118336</v>
       </c>
       <c r="Q78">
-        <v>-10.03447968</v>
+        <v>-10.46118336</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1860045552532569</v>
+        <v>0.1921004054816594</v>
       </c>
       <c r="T78">
-        <v>2.567895667269434</v>
+        <v>2.679543304976801</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1424090070383763</v>
+        <v>0.1405595394145012</v>
       </c>
       <c r="W78">
-        <v>0.2022199561403509</v>
+        <v>0.2026560606060606</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4068828772525036</v>
+        <v>0.4015986840414322</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2002282599274484</v>
+        <v>0.2021282599274483</v>
       </c>
       <c r="C79">
-        <v>-147.3381412687758</v>
+        <v>-150.905459215551</v>
       </c>
       <c r="D79">
-        <v>64.44985873122423</v>
+        <v>63.66654078444893</v>
       </c>
       <c r="E79">
-        <v>185.668</v>
+        <v>188.452</v>
       </c>
       <c r="F79">
-        <v>214.368</v>
+        <v>217.152</v>
       </c>
       <c r="G79">
         <v>2.58</v>
@@ -7765,37 +7765,37 @@
         <v>20.3</v>
       </c>
       <c r="M79">
-        <v>50.5479744</v>
+        <v>51.2044416</v>
       </c>
       <c r="N79">
-        <v>-30.2479744</v>
+        <v>-30.90444159999999</v>
       </c>
       <c r="O79">
-        <v>-10.58679104</v>
+        <v>-10.81655456</v>
       </c>
       <c r="P79">
-        <v>-19.66118336</v>
+        <v>-20.08788704</v>
       </c>
       <c r="Q79">
-        <v>-10.46118336</v>
+        <v>-10.88788704</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1921004054816594</v>
+        <v>0.1987504239126439</v>
       </c>
       <c r="T79">
-        <v>2.679543304976801</v>
+        <v>2.801340727930292</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1405595394145012</v>
+        <v>0.1387574940373923</v>
       </c>
       <c r="W79">
-        <v>0.2026560606060606</v>
+        <v>0.2030809829059829</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4015986840414322</v>
+        <v>0.3964499829639779</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2021282599274483</v>
+        <v>0.2040282599274484</v>
       </c>
       <c r="C80">
-        <v>-150.905459215551</v>
+        <v>-154.4539650474797</v>
       </c>
       <c r="D80">
-        <v>63.66654078444893</v>
+        <v>62.9020349525203</v>
       </c>
       <c r="E80">
-        <v>188.452</v>
+        <v>191.236</v>
       </c>
       <c r="F80">
-        <v>217.152</v>
+        <v>219.936</v>
       </c>
       <c r="G80">
         <v>2.58</v>
@@ -7847,37 +7847,37 @@
         <v>20.3</v>
       </c>
       <c r="M80">
-        <v>51.2044416</v>
+        <v>51.8609088</v>
       </c>
       <c r="N80">
-        <v>-30.90444159999999</v>
+        <v>-31.5609088</v>
       </c>
       <c r="O80">
-        <v>-10.81655456</v>
+        <v>-11.04631808</v>
       </c>
       <c r="P80">
-        <v>-20.08788704</v>
+        <v>-20.51459072</v>
       </c>
       <c r="Q80">
-        <v>-10.88788704</v>
+        <v>-11.31459072</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1987504239126439</v>
+        <v>0.2060337774322936</v>
       </c>
       <c r="T80">
-        <v>2.801340727930292</v>
+        <v>2.934737905450782</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1387574940373923</v>
+        <v>0.1370010700622354</v>
       </c>
       <c r="W80">
-        <v>0.2030809829059829</v>
+        <v>0.2034951476793249</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3964499829639779</v>
+        <v>0.391431628749244</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2040282599274484</v>
+        <v>0.2059282599274483</v>
       </c>
       <c r="C81">
-        <v>-154.4539650474797</v>
+        <v>-157.9843284093494</v>
       </c>
       <c r="D81">
-        <v>62.9020349525203</v>
+        <v>62.15567159065063</v>
       </c>
       <c r="E81">
-        <v>191.236</v>
+        <v>194.02</v>
       </c>
       <c r="F81">
-        <v>219.936</v>
+        <v>222.72</v>
       </c>
       <c r="G81">
         <v>2.58</v>
@@ -7929,37 +7929,37 @@
         <v>20.3</v>
       </c>
       <c r="M81">
-        <v>51.8609088</v>
+        <v>52.517376</v>
       </c>
       <c r="N81">
-        <v>-31.5609088</v>
+        <v>-32.217376</v>
       </c>
       <c r="O81">
-        <v>-11.04631808</v>
+        <v>-11.2760816</v>
       </c>
       <c r="P81">
-        <v>-20.51459072</v>
+        <v>-20.9412944</v>
       </c>
       <c r="Q81">
-        <v>-11.31459072</v>
+        <v>-11.7412944</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2060337774322936</v>
+        <v>0.2140454663039083</v>
       </c>
       <c r="T81">
-        <v>2.934737905450782</v>
+        <v>3.081474800723321</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1370010700622354</v>
+        <v>0.1352885566864575</v>
       </c>
       <c r="W81">
-        <v>0.2034951476793249</v>
+        <v>0.2038989583333334</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.391431628749244</v>
+        <v>0.3865387333898784</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2059282599274483</v>
+        <v>0.2078282599274484</v>
       </c>
       <c r="C82">
-        <v>-157.9843284093494</v>
+        <v>-161.4971875359925</v>
       </c>
       <c r="D82">
-        <v>62.15567159065063</v>
+        <v>61.42681246400745</v>
       </c>
       <c r="E82">
-        <v>194.02</v>
+        <v>196.804</v>
       </c>
       <c r="F82">
-        <v>222.72</v>
+        <v>225.504</v>
       </c>
       <c r="G82">
         <v>2.58</v>
@@ -8011,37 +8011,37 @@
         <v>20.3</v>
       </c>
       <c r="M82">
-        <v>52.517376</v>
+        <v>53.1738432</v>
       </c>
       <c r="N82">
-        <v>-32.217376</v>
+        <v>-32.8738432</v>
       </c>
       <c r="O82">
-        <v>-11.2760816</v>
+        <v>-11.50584512</v>
       </c>
       <c r="P82">
-        <v>-20.9412944</v>
+        <v>-21.36799808</v>
       </c>
       <c r="Q82">
-        <v>-11.7412944</v>
+        <v>-12.16799808</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2140454663039083</v>
+        <v>0.2229004908462192</v>
       </c>
       <c r="T82">
-        <v>3.081474800723321</v>
+        <v>3.243657684971918</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1352885566864575</v>
+        <v>0.1336183275915629</v>
       </c>
       <c r="W82">
-        <v>0.2038989583333334</v>
+        <v>0.2042927983539095</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3865387333898784</v>
+        <v>0.3817666502616084</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2078282599274484</v>
+        <v>0.2097282599274483</v>
       </c>
       <c r="C83">
-        <v>-161.4971875359925</v>
+        <v>-164.9931510725619</v>
       </c>
       <c r="D83">
-        <v>61.42681246400745</v>
+        <v>60.71484892743806</v>
       </c>
       <c r="E83">
-        <v>196.804</v>
+        <v>199.588</v>
       </c>
       <c r="F83">
-        <v>225.504</v>
+        <v>228.288</v>
       </c>
       <c r="G83">
         <v>2.58</v>
@@ -8093,37 +8093,37 @@
         <v>20.3</v>
       </c>
       <c r="M83">
-        <v>53.1738432</v>
+        <v>53.8303104</v>
       </c>
       <c r="N83">
-        <v>-32.8738432</v>
+        <v>-33.5303104</v>
       </c>
       <c r="O83">
-        <v>-11.50584512</v>
+        <v>-11.73560864</v>
       </c>
       <c r="P83">
-        <v>-21.36799808</v>
+        <v>-21.79470176</v>
       </c>
       <c r="Q83">
-        <v>-12.16799808</v>
+        <v>-12.59470176</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2229004908462192</v>
+        <v>0.2327394070043425</v>
       </c>
       <c r="T83">
-        <v>3.243657684971918</v>
+        <v>3.42386088969258</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1336183275915629</v>
+        <v>0.1319888357916658</v>
       </c>
       <c r="W83">
-        <v>0.2042927983539095</v>
+        <v>0.2046770325203252</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3817666502616084</v>
+        <v>0.3771109594047594</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2097282599274483</v>
+        <v>0.2116282599274484</v>
       </c>
       <c r="C84">
-        <v>-164.9931510725619</v>
+        <v>-168.4727997696695</v>
       </c>
       <c r="D84">
-        <v>60.71484892743806</v>
+        <v>60.01920023033055</v>
       </c>
       <c r="E84">
-        <v>199.588</v>
+        <v>202.372</v>
       </c>
       <c r="F84">
-        <v>228.288</v>
+        <v>231.072</v>
       </c>
       <c r="G84">
         <v>2.58</v>
@@ -8175,37 +8175,37 @@
         <v>20.3</v>
       </c>
       <c r="M84">
-        <v>53.8303104</v>
+        <v>54.4867776</v>
       </c>
       <c r="N84">
-        <v>-33.5303104</v>
+        <v>-34.1867776</v>
       </c>
       <c r="O84">
-        <v>-11.73560864</v>
+        <v>-11.96537216</v>
       </c>
       <c r="P84">
-        <v>-21.79470176</v>
+        <v>-22.22140544</v>
       </c>
       <c r="Q84">
-        <v>-12.59470176</v>
+        <v>-13.02140544</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2327394070043425</v>
+        <v>0.2437358427104803</v>
       </c>
       <c r="T84">
-        <v>3.42386088969258</v>
+        <v>3.625264471439202</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1319888357916658</v>
+        <v>0.1303986088544168</v>
       </c>
       <c r="W84">
-        <v>0.2046770325203252</v>
+        <v>0.2050520080321285</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3771109594047594</v>
+        <v>0.3725674538697624</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2116282599274484</v>
+        <v>0.2135282599274483</v>
       </c>
       <c r="C85">
-        <v>-168.4727997696695</v>
+        <v>-171.9366880633115</v>
       </c>
       <c r="D85">
-        <v>60.01920023033055</v>
+        <v>59.33931193668847</v>
       </c>
       <c r="E85">
-        <v>202.372</v>
+        <v>205.156</v>
       </c>
       <c r="F85">
-        <v>231.072</v>
+        <v>233.856</v>
       </c>
       <c r="G85">
         <v>2.58</v>
@@ -8257,37 +8257,37 @@
         <v>20.3</v>
       </c>
       <c r="M85">
-        <v>54.4867776</v>
+        <v>55.1432448</v>
       </c>
       <c r="N85">
-        <v>-34.1867776</v>
+        <v>-34.84324479999999</v>
       </c>
       <c r="O85">
-        <v>-11.96537216</v>
+        <v>-12.19513568</v>
       </c>
       <c r="P85">
-        <v>-22.22140544</v>
+        <v>-22.64810912</v>
       </c>
       <c r="Q85">
-        <v>-13.02140544</v>
+        <v>-13.44810912</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2437358427104803</v>
+        <v>0.2561068328798854</v>
       </c>
       <c r="T85">
-        <v>3.625264471439202</v>
+        <v>3.851843500904153</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1303986088544168</v>
+        <v>0.1288462444632928</v>
       </c>
       <c r="W85">
-        <v>0.2050520080321285</v>
+        <v>0.2054180555555556</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3725674538697624</v>
+        <v>0.3681321270379796</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2135282599274483</v>
+        <v>0.2154282599274483</v>
       </c>
       <c r="C86">
-        <v>-171.9366880633115</v>
+        <v>-175.3853455486145</v>
       </c>
       <c r="D86">
-        <v>59.3393119366885</v>
+        <v>58.67465445138545</v>
       </c>
       <c r="E86">
-        <v>205.156</v>
+        <v>207.94</v>
       </c>
       <c r="F86">
-        <v>233.856</v>
+        <v>236.64</v>
       </c>
       <c r="G86">
         <v>2.58</v>
@@ -8339,37 +8339,37 @@
         <v>20.3</v>
       </c>
       <c r="M86">
-        <v>55.14324479999999</v>
+        <v>55.799712</v>
       </c>
       <c r="N86">
-        <v>-34.84324479999999</v>
+        <v>-35.499712</v>
       </c>
       <c r="O86">
-        <v>-12.19513568</v>
+        <v>-12.4248992</v>
       </c>
       <c r="P86">
-        <v>-22.64810912</v>
+        <v>-23.0748128</v>
       </c>
       <c r="Q86">
-        <v>-13.44810912</v>
+        <v>-13.8748128</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2561068328798852</v>
+        <v>0.270127288405211</v>
       </c>
       <c r="T86">
-        <v>3.85184350090415</v>
+        <v>4.108633067631095</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1288462444632928</v>
+        <v>0.1273304062931364</v>
       </c>
       <c r="W86">
-        <v>0.2054180555555556</v>
+        <v>0.2057754901960784</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3681321270379795</v>
+        <v>0.3638011608375326</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2154282599274483</v>
+        <v>0.2173282599274483</v>
       </c>
       <c r="C87">
-        <v>-175.3853455486145</v>
+        <v>-178.8192783556329</v>
       </c>
       <c r="D87">
-        <v>58.67465445138545</v>
+        <v>58.02472164436703</v>
       </c>
       <c r="E87">
-        <v>207.94</v>
+        <v>210.724</v>
       </c>
       <c r="F87">
-        <v>236.64</v>
+        <v>239.424</v>
       </c>
       <c r="G87">
         <v>2.58</v>
@@ -8421,37 +8421,37 @@
         <v>20.3</v>
       </c>
       <c r="M87">
-        <v>55.799712</v>
+        <v>56.45617919999999</v>
       </c>
       <c r="N87">
-        <v>-35.499712</v>
+        <v>-36.1561792</v>
       </c>
       <c r="O87">
-        <v>-12.4248992</v>
+        <v>-12.65466272</v>
       </c>
       <c r="P87">
-        <v>-23.0748128</v>
+        <v>-23.50151648</v>
       </c>
       <c r="Q87">
-        <v>-13.8748128</v>
+        <v>-14.30151648</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.270127288405211</v>
+        <v>0.2861506661484403</v>
       </c>
       <c r="T87">
-        <v>4.108633067631095</v>
+        <v>4.402106858176173</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1273304062931364</v>
+        <v>0.1258498201734488</v>
       </c>
       <c r="W87">
-        <v>0.2057754901960784</v>
+        <v>0.2061246124031008</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3638011608375326</v>
+        <v>0.3595709147812822</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2173282599274483</v>
+        <v>0.2192282599274483</v>
       </c>
       <c r="C88">
-        <v>-178.8192783556329</v>
+        <v>-182.2389704347117</v>
       </c>
       <c r="D88">
-        <v>58.02472164436703</v>
+        <v>57.38902956528823</v>
       </c>
       <c r="E88">
-        <v>210.724</v>
+        <v>213.508</v>
       </c>
       <c r="F88">
-        <v>239.424</v>
+        <v>242.208</v>
       </c>
       <c r="G88">
         <v>2.58</v>
@@ -8503,37 +8503,37 @@
         <v>20.3</v>
       </c>
       <c r="M88">
-        <v>56.45617919999999</v>
+        <v>57.1126464</v>
       </c>
       <c r="N88">
-        <v>-36.1561792</v>
+        <v>-36.81264639999999</v>
       </c>
       <c r="O88">
-        <v>-12.65466272</v>
+        <v>-12.88442624</v>
       </c>
       <c r="P88">
-        <v>-23.50151648</v>
+        <v>-23.92822016</v>
       </c>
       <c r="Q88">
-        <v>-14.30151648</v>
+        <v>-14.72822016</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2861506661484403</v>
+        <v>0.3046391789290896</v>
       </c>
       <c r="T88">
-        <v>4.402106858176173</v>
+        <v>4.740730462651262</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1258498201734488</v>
+        <v>0.1244032705162827</v>
       </c>
       <c r="W88">
-        <v>0.2061246124031008</v>
+        <v>0.2064657088122605</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3595709147812822</v>
+        <v>0.3554379157608079</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2192282599274483</v>
+        <v>0.2211282599274483</v>
       </c>
       <c r="C89">
-        <v>-182.2389704347117</v>
+        <v>-185.6448847582736</v>
       </c>
       <c r="D89">
-        <v>57.38902956528823</v>
+        <v>56.76711524172641</v>
       </c>
       <c r="E89">
-        <v>213.508</v>
+        <v>216.292</v>
       </c>
       <c r="F89">
-        <v>242.208</v>
+        <v>244.992</v>
       </c>
       <c r="G89">
         <v>2.58</v>
@@ -8585,37 +8585,37 @@
         <v>20.3</v>
       </c>
       <c r="M89">
-        <v>57.1126464</v>
+        <v>57.7691136</v>
       </c>
       <c r="N89">
-        <v>-36.81264639999999</v>
+        <v>-37.4691136</v>
       </c>
       <c r="O89">
-        <v>-12.88442624</v>
+        <v>-13.11418976</v>
       </c>
       <c r="P89">
-        <v>-23.92822016</v>
+        <v>-24.35492384</v>
       </c>
       <c r="Q89">
-        <v>-14.72822016</v>
+        <v>-15.15492384</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3046391789290896</v>
+        <v>0.3262091105065137</v>
       </c>
       <c r="T89">
-        <v>4.740730462651262</v>
+        <v>5.135791334538868</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1244032705162827</v>
+        <v>0.1229895969876886</v>
       </c>
       <c r="W89">
-        <v>0.2064657088122605</v>
+        <v>0.206799053030303</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3554379157608079</v>
+        <v>0.3513988485362531</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2211282599274483</v>
+        <v>0.2230282599274483</v>
       </c>
       <c r="C90">
-        <v>-185.6448847582736</v>
+        <v>-189.0374644453022</v>
       </c>
       <c r="D90">
-        <v>56.76711524172641</v>
+        <v>56.15853555469775</v>
       </c>
       <c r="E90">
-        <v>216.292</v>
+        <v>219.076</v>
       </c>
       <c r="F90">
-        <v>244.992</v>
+        <v>247.776</v>
       </c>
       <c r="G90">
         <v>2.58</v>
@@ -8667,37 +8667,37 @@
         <v>20.3</v>
       </c>
       <c r="M90">
-        <v>57.7691136</v>
+        <v>58.4255808</v>
       </c>
       <c r="N90">
-        <v>-37.4691136</v>
+        <v>-38.12558079999999</v>
       </c>
       <c r="O90">
-        <v>-13.11418976</v>
+        <v>-13.34395328</v>
       </c>
       <c r="P90">
-        <v>-24.35492384</v>
+        <v>-24.78162752</v>
       </c>
       <c r="Q90">
-        <v>-15.15492384</v>
+        <v>-15.58162752</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3262091105065137</v>
+        <v>0.3517008478252877</v>
       </c>
       <c r="T90">
-        <v>5.135791334538868</v>
+        <v>5.602681455860584</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1229895969876886</v>
+        <v>0.1216076914035573</v>
       </c>
       <c r="W90">
-        <v>0.206799053030303</v>
+        <v>0.2071249063670412</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3513988485362531</v>
+        <v>0.3474505468673066</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2230282599274483</v>
+        <v>0.2249282599274483</v>
       </c>
       <c r="C91">
-        <v>-189.0374644453022</v>
+        <v>-192.4171338142625</v>
       </c>
       <c r="D91">
-        <v>56.15853555469775</v>
+        <v>55.56286618573753</v>
       </c>
       <c r="E91">
-        <v>219.076</v>
+        <v>221.86</v>
       </c>
       <c r="F91">
-        <v>247.776</v>
+        <v>250.56</v>
       </c>
       <c r="G91">
         <v>2.58</v>
@@ -8749,37 +8749,37 @@
         <v>20.3</v>
       </c>
       <c r="M91">
-        <v>58.4255808</v>
+        <v>59.08204799999999</v>
       </c>
       <c r="N91">
-        <v>-38.12558079999999</v>
+        <v>-38.78204799999999</v>
       </c>
       <c r="O91">
-        <v>-13.34395328</v>
+        <v>-13.5737168</v>
       </c>
       <c r="P91">
-        <v>-24.78162752</v>
+        <v>-25.20833119999999</v>
       </c>
       <c r="Q91">
-        <v>-15.58162752</v>
+        <v>-16.00833119999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3517008478252877</v>
+        <v>0.3822909326078165</v>
       </c>
       <c r="T91">
-        <v>5.602681455860584</v>
+        <v>6.162949601446643</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1216076914035573</v>
+        <v>0.1202564948324066</v>
       </c>
       <c r="W91">
-        <v>0.2071249063670412</v>
+        <v>0.2074435185185185</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3474505468673066</v>
+        <v>0.3435899852354476</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2249282599274483</v>
+        <v>0.2268282599274483</v>
       </c>
       <c r="C92">
-        <v>-192.4171338142625</v>
+        <v>-195.7842993697134</v>
       </c>
       <c r="D92">
-        <v>55.56286618573753</v>
+        <v>54.97970063028661</v>
       </c>
       <c r="E92">
-        <v>221.86</v>
+        <v>224.644</v>
       </c>
       <c r="F92">
-        <v>250.56</v>
+        <v>253.344</v>
       </c>
       <c r="G92">
         <v>2.58</v>
@@ -8831,37 +8831,37 @@
         <v>20.3</v>
       </c>
       <c r="M92">
-        <v>59.08204799999999</v>
+        <v>59.7385152</v>
       </c>
       <c r="N92">
-        <v>-38.78204799999999</v>
+        <v>-39.4385152</v>
       </c>
       <c r="O92">
-        <v>-13.5737168</v>
+        <v>-13.80348032</v>
       </c>
       <c r="P92">
-        <v>-25.20833119999999</v>
+        <v>-25.63503488</v>
       </c>
       <c r="Q92">
-        <v>-16.00833119999999</v>
+        <v>-16.43503488</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3822909326078165</v>
+        <v>0.4196788140086851</v>
       </c>
       <c r="T92">
-        <v>6.162949601446643</v>
+        <v>6.847721779385159</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1202564948324066</v>
+        <v>0.1189349948891934</v>
       </c>
       <c r="W92">
-        <v>0.2074435185185185</v>
+        <v>0.2077551282051282</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3435899852354476</v>
+        <v>0.3398142711119811</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2268282599274483</v>
+        <v>0.2287282599274483</v>
       </c>
       <c r="C93">
-        <v>-195.7842993697134</v>
+        <v>-199.1393507274367</v>
       </c>
       <c r="D93">
-        <v>54.97970063028661</v>
+        <v>54.40864927256325</v>
       </c>
       <c r="E93">
-        <v>224.644</v>
+        <v>227.428</v>
       </c>
       <c r="F93">
-        <v>253.344</v>
+        <v>256.128</v>
       </c>
       <c r="G93">
         <v>2.58</v>
@@ -8913,37 +8913,37 @@
         <v>20.3</v>
       </c>
       <c r="M93">
-        <v>59.7385152</v>
+        <v>60.3949824</v>
       </c>
       <c r="N93">
-        <v>-39.4385152</v>
+        <v>-40.09498239999999</v>
       </c>
       <c r="O93">
-        <v>-13.80348032</v>
+        <v>-14.03324384</v>
       </c>
       <c r="P93">
-        <v>-25.63503488</v>
+        <v>-26.06173855999999</v>
       </c>
       <c r="Q93">
-        <v>-16.43503488</v>
+        <v>-16.86173856</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4196788140086851</v>
+        <v>0.4664136657597708</v>
       </c>
       <c r="T93">
-        <v>6.847721779385159</v>
+        <v>7.703687001808307</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1189349948891934</v>
+        <v>0.1176422232056152</v>
       </c>
       <c r="W93">
-        <v>0.2077551282051282</v>
+        <v>0.208059963768116</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3398142711119811</v>
+        <v>0.3361206377303292</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2287282599274483</v>
+        <v>0.2306282599274483</v>
       </c>
       <c r="C94">
-        <v>-199.1393507274367</v>
+        <v>-202.4826614825044</v>
       </c>
       <c r="D94">
-        <v>54.40864927256325</v>
+        <v>53.84933851749557</v>
       </c>
       <c r="E94">
-        <v>227.428</v>
+        <v>230.212</v>
       </c>
       <c r="F94">
-        <v>256.128</v>
+        <v>258.912</v>
       </c>
       <c r="G94">
         <v>2.58</v>
@@ -8995,37 +8995,37 @@
         <v>20.3</v>
       </c>
       <c r="M94">
-        <v>60.3949824</v>
+        <v>61.0514496</v>
       </c>
       <c r="N94">
-        <v>-40.09498239999999</v>
+        <v>-40.7514496</v>
       </c>
       <c r="O94">
-        <v>-14.03324384</v>
+        <v>-14.26300736</v>
       </c>
       <c r="P94">
-        <v>-26.06173855999999</v>
+        <v>-26.48844224</v>
       </c>
       <c r="Q94">
-        <v>-16.86173856</v>
+        <v>-17.28844224</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4664136657597708</v>
+        <v>0.5265013322968809</v>
       </c>
       <c r="T94">
-        <v>7.703687001808307</v>
+        <v>8.804213716352351</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1176422232056152</v>
+        <v>0.1163772530636193</v>
       </c>
       <c r="W94">
-        <v>0.208059963768116</v>
+        <v>0.2083582437275986</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3361206377303292</v>
+        <v>0.3325064373246266</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2306282599274483</v>
+        <v>0.2325282599274483</v>
       </c>
       <c r="C95">
-        <v>-202.4826614825044</v>
+        <v>-205.8145900243491</v>
       </c>
       <c r="D95">
-        <v>53.84933851749557</v>
+        <v>53.30140997565088</v>
       </c>
       <c r="E95">
-        <v>230.212</v>
+        <v>232.996</v>
       </c>
       <c r="F95">
-        <v>258.912</v>
+        <v>261.696</v>
       </c>
       <c r="G95">
         <v>2.58</v>
@@ -9077,37 +9077,37 @@
         <v>20.3</v>
       </c>
       <c r="M95">
-        <v>61.0514496</v>
+        <v>61.70791679999999</v>
       </c>
       <c r="N95">
-        <v>-40.7514496</v>
+        <v>-41.4079168</v>
       </c>
       <c r="O95">
-        <v>-14.26300736</v>
+        <v>-14.49277088</v>
       </c>
       <c r="P95">
-        <v>-26.48844224</v>
+        <v>-26.91514592</v>
       </c>
       <c r="Q95">
-        <v>-17.28844224</v>
+        <v>-17.71514592</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5265013322968809</v>
+        <v>0.606618221013028</v>
       </c>
       <c r="T95">
-        <v>8.804213716352351</v>
+        <v>10.27158266907775</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1163772530636193</v>
+        <v>0.1151391971799638</v>
       </c>
       <c r="W95">
-        <v>0.2083582437275986</v>
+        <v>0.2086501773049645</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3325064373246266</v>
+        <v>0.3289691347998965</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2325282599274483</v>
+        <v>0.2344282599274483</v>
       </c>
       <c r="C96">
-        <v>-205.8145900243491</v>
+        <v>-209.1354803025752</v>
       </c>
       <c r="D96">
-        <v>53.30140997565088</v>
+        <v>52.76451969742484</v>
       </c>
       <c r="E96">
-        <v>232.996</v>
+        <v>235.78</v>
       </c>
       <c r="F96">
-        <v>261.696</v>
+        <v>264.48</v>
       </c>
       <c r="G96">
         <v>2.58</v>
@@ -9159,37 +9159,37 @@
         <v>20.3</v>
       </c>
       <c r="M96">
-        <v>61.70791679999999</v>
+        <v>62.36438400000001</v>
       </c>
       <c r="N96">
-        <v>-41.4079168</v>
+        <v>-42.064384</v>
       </c>
       <c r="O96">
-        <v>-14.49277088</v>
+        <v>-14.7225344</v>
       </c>
       <c r="P96">
-        <v>-26.91514592</v>
+        <v>-27.3418496</v>
       </c>
       <c r="Q96">
-        <v>-17.71514592</v>
+        <v>-18.1418496</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.606618221013028</v>
+        <v>0.7187818652156338</v>
       </c>
       <c r="T96">
-        <v>10.27158266907775</v>
+        <v>12.3258992028933</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1151391971799638</v>
+        <v>0.113927205630701</v>
       </c>
       <c r="W96">
-        <v>0.2086501773049645</v>
+        <v>0.2089359649122807</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3289691347998965</v>
+        <v>0.3255063018020029</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2344282599274483</v>
+        <v>0.2363282599274483</v>
       </c>
       <c r="C97">
-        <v>-209.1354803025752</v>
+        <v>-212.4456625469481</v>
       </c>
       <c r="D97">
-        <v>52.76451969742484</v>
+        <v>52.23833745305186</v>
       </c>
       <c r="E97">
-        <v>235.78</v>
+        <v>238.564</v>
       </c>
       <c r="F97">
-        <v>264.48</v>
+        <v>267.264</v>
       </c>
       <c r="G97">
         <v>2.58</v>
@@ -9241,37 +9241,37 @@
         <v>20.3</v>
       </c>
       <c r="M97">
-        <v>62.36438400000001</v>
+        <v>63.0208512</v>
       </c>
       <c r="N97">
-        <v>-42.064384</v>
+        <v>-42.7208512</v>
       </c>
       <c r="O97">
-        <v>-14.7225344</v>
+        <v>-14.95229792</v>
       </c>
       <c r="P97">
-        <v>-27.3418496</v>
+        <v>-27.76855328</v>
       </c>
       <c r="Q97">
-        <v>-18.1418496</v>
+        <v>-18.56855328</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7187818652156338</v>
+        <v>0.8870273315195427</v>
       </c>
       <c r="T97">
-        <v>12.3258992028933</v>
+        <v>15.40737400361663</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.113927205630701</v>
+        <v>0.1127404639053812</v>
       </c>
       <c r="W97">
-        <v>0.2089359649122807</v>
+        <v>0.2092157986111111</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3255063018020029</v>
+        <v>0.3221156111582321</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2363282599274483</v>
+        <v>0.2382282599274483</v>
       </c>
       <c r="C98">
-        <v>-212.4456625469481</v>
+        <v>-215.7454539447304</v>
       </c>
       <c r="D98">
-        <v>52.23833745305186</v>
+        <v>51.72254605526953</v>
       </c>
       <c r="E98">
-        <v>238.564</v>
+        <v>241.348</v>
       </c>
       <c r="F98">
-        <v>267.264</v>
+        <v>270.0479999999999</v>
       </c>
       <c r="G98">
         <v>2.58</v>
@@ -9323,37 +9323,37 @@
         <v>20.3</v>
       </c>
       <c r="M98">
-        <v>63.02085119999999</v>
+        <v>63.67731839999999</v>
       </c>
       <c r="N98">
-        <v>-42.72085119999998</v>
+        <v>-43.37731839999999</v>
       </c>
       <c r="O98">
-        <v>-14.95229791999999</v>
+        <v>-15.18206144</v>
       </c>
       <c r="P98">
-        <v>-27.76855327999999</v>
+        <v>-28.19525695999999</v>
       </c>
       <c r="Q98">
-        <v>-18.56855327999999</v>
+        <v>-18.99525696</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8870273315195404</v>
+        <v>1.167436442026054</v>
       </c>
       <c r="T98">
-        <v>15.40737400361659</v>
+        <v>20.54316533815546</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1127404639053812</v>
+        <v>0.1115781910816144</v>
       </c>
       <c r="W98">
-        <v>0.2092157986111111</v>
+        <v>0.2094898625429553</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3221156111582322</v>
+        <v>0.3187948316617554</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2382282599274483</v>
+        <v>0.2401282599274484</v>
       </c>
       <c r="C99">
-        <v>-215.7454539447304</v>
+        <v>-219.0351592782816</v>
       </c>
       <c r="D99">
-        <v>51.72254605526953</v>
+        <v>51.21684072171844</v>
       </c>
       <c r="E99">
-        <v>241.348</v>
+        <v>244.132</v>
       </c>
       <c r="F99">
-        <v>270.0479999999999</v>
+        <v>272.832</v>
       </c>
       <c r="G99">
         <v>2.58</v>
@@ -9405,37 +9405,37 @@
         <v>20.3</v>
       </c>
       <c r="M99">
-        <v>63.67731839999999</v>
+        <v>64.3337856</v>
       </c>
       <c r="N99">
-        <v>-43.37731839999999</v>
+        <v>-44.0337856</v>
       </c>
       <c r="O99">
-        <v>-15.18206144</v>
+        <v>-15.41182496</v>
       </c>
       <c r="P99">
-        <v>-28.19525695999999</v>
+        <v>-28.62196064</v>
       </c>
       <c r="Q99">
-        <v>-18.99525696</v>
+        <v>-19.42196064000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.167436442026054</v>
+        <v>1.728254663039081</v>
       </c>
       <c r="T99">
-        <v>20.54316533815546</v>
+        <v>30.81474800723318</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1115781910816144</v>
+        <v>0.1104396381113938</v>
       </c>
       <c r="W99">
-        <v>0.2094898625429553</v>
+        <v>0.2097583333333334</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3187948316617554</v>
+        <v>0.3155418231754109</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2401282599274484</v>
+        <v>0.2420282599274483</v>
       </c>
       <c r="C100">
-        <v>-219.0351592782816</v>
+        <v>-222.3150715256166</v>
       </c>
       <c r="D100">
-        <v>51.21684072171844</v>
+        <v>50.72092847438342</v>
       </c>
       <c r="E100">
-        <v>244.132</v>
+        <v>246.916</v>
       </c>
       <c r="F100">
-        <v>272.832</v>
+        <v>275.616</v>
       </c>
       <c r="G100">
         <v>2.58</v>
@@ -9487,37 +9487,37 @@
         <v>20.3</v>
       </c>
       <c r="M100">
-        <v>64.3337856</v>
+        <v>64.99025279999999</v>
       </c>
       <c r="N100">
-        <v>-44.0337856</v>
+        <v>-44.6902528</v>
       </c>
       <c r="O100">
-        <v>-15.41182496</v>
+        <v>-15.64158848</v>
       </c>
       <c r="P100">
-        <v>-28.62196064</v>
+        <v>-29.04866432</v>
       </c>
       <c r="Q100">
-        <v>-19.42196064000001</v>
+        <v>-19.84866432</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.728254663039081</v>
+        <v>3.410709326078162</v>
       </c>
       <c r="T100">
-        <v>30.81474800723318</v>
+        <v>61.62949601446636</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1104396381113938</v>
+        <v>0.1093240862112787</v>
       </c>
       <c r="W100">
-        <v>0.2097583333333334</v>
+        <v>0.2100213804713805</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3155418231754109</v>
+        <v>0.312354532032225</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2420282599274483</v>
-      </c>
-      <c r="C101">
-        <v>-222.3150715256166</v>
-      </c>
-      <c r="D101">
-        <v>50.72092847438342</v>
-      </c>
-      <c r="E101">
-        <v>246.916</v>
-      </c>
-      <c r="F101">
-        <v>275.616</v>
-      </c>
-      <c r="G101">
-        <v>2.58</v>
-      </c>
-      <c r="H101">
-        <v>249.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>29.5</v>
-      </c>
-      <c r="K101">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="L101">
-        <v>20.3</v>
-      </c>
-      <c r="M101">
-        <v>64.99025279999999</v>
-      </c>
-      <c r="N101">
-        <v>-44.6902528</v>
-      </c>
-      <c r="O101">
-        <v>-15.64158848</v>
-      </c>
-      <c r="P101">
-        <v>-29.04866432</v>
-      </c>
-      <c r="Q101">
-        <v>-19.84866432</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.410709326078162</v>
-      </c>
-      <c r="T101">
-        <v>61.62949601446636</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1093240862112787</v>
-      </c>
-      <c r="W101">
-        <v>0.2100213804713805</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.312354532032225</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
